--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y80"/>
+  <dimension ref="A1:Y84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Mar 31</t>
+          <t>Sun, Apr 7</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 1</t>
+          <t>Mon, Apr 8</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 2</t>
+          <t>Tue, Apr 9</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Apr 3</t>
+          <t>Wed, Apr 10</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Apr 4</t>
+          <t>Thu, Apr 11</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Apr 5</t>
+          <t>Fri, Apr 12</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Apr 6</t>
+          <t>Sat, Apr 13</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>5:15 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -669,7 +669,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -685,7 +685,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t>5:00 AM MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -693,7 +693,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET BAYSHORE</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -732,7 +732,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -755,7 +755,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OUTPOST NATURAL FOODS, BAY VIEW</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -779,7 +779,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -802,7 +802,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2826 S KINNICKINNC AVE</t>
+          <t>FESTIVAL #2702, MANITOWOC - LIFO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -810,8 +810,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PICK #856, RACINE-
-MT PLEASANT</t>
+          <t>MARIANO'S #520 +RX, CHICAGO-BRIDGEPORT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -819,7 +818,8 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #522 +RX, CHICAGO-EDGEWATER</t>
+          <t>MARIANO'S #534 +RX, 
+NEW CITY</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -827,7 +827,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>FESTIVAL #2732, APPLETON - NORTHLAND - LIFO</t>
+          <t>AURORA OUTPATIENT RX #1174 WALWORTH</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -835,7 +835,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>PICK #408, TWO RIVERS</t>
+          <t>MARIANO'S #532 +RX, GLENVIEW</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -850,7 +850,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5hiyyxywjiH2</t>
+          <t>2151 S 42ND ST</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -858,7 +858,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1202  N GREENBAY RD</t>
+          <t>3145 S ASHLAND AVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -866,7 +866,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5201 N SHERIDAN RD</t>
+          <t>1500 N CLYBOURN AVE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -874,7 +874,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1200 W NORTHLAND AVE</t>
+          <t>525 KENOSHA ST, SUITE C</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -882,7 +882,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1010 22ND STREET</t>
+          <t>2323 CAPITAL DR</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -895,13 +895,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/ynTuKFekbGQ2</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/gCMavYTDGoo</t>
+          <t>https://goo.gl/maps/8Wt7uwiJSHJ2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -909,7 +913,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/9eaE3Q6o8jF2</t>
+          <t>https://goo.gl/maps/jSfCth27mhJ2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -917,7 +921,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/eRWs6b1N24m</t>
+          <t>https://goo.gl/maps/HYXAm9E8G2X4pAUGA</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -925,7 +929,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/5jsT8sqpo6yELUmX9</t>
+          <t>https://goo.gl/maps/ut53mE2zZpL2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -937,21 +941,9 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
@@ -962,7 +954,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SET UP ON REG #7</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -972,7 +968,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>DJ and Mai will start here, Aurora is 10 min away, 7:30 Start</t>
+          <t>SET UP ON REG #2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -986,39 +982,32 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Kim G</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>*Kim - Lincoln - Sonia meet at the office @ 4:45 am</t>
+          <t xml:space="preserve">NEW FROZEN DRS, BUT NO MAJOR PRODUCT CHANGES PER PAUL </t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1027,21 +1016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Ian's car to pick up Carlie on the way north @ Grafton</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
@@ -1053,15 +1038,20 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>@ Store,
+Optima</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1069,15 +1059,19 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1086,19 +1080,31 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>Driver,
-Optima</t>
+Camry</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
     </row>
@@ -1109,12 +1115,12 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1126,61 +1132,47 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Kim G</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>*Driver
-Sante Fe, Equip</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
@@ -1189,8 +1181,16 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
@@ -1200,53 +1200,41 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>@ Grafton</t>
+          <t>Driver,
+Camry</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -1257,9 +1245,22 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
@@ -1268,52 +1269,56 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Driver,
-Sante Fe,
-Rx</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>4:30 AM MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
     </row>
@@ -1322,13 +1327,22 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
@@ -1337,53 +1351,45 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>3rd week</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Kim G</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Kim G</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>w/ Mai
-Aurora @ 7:30</t>
+          <t>Driver,
+Sante Fe</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -1394,10 +1400,14 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1409,60 +1419,46 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Kim C</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>3rd scan, work w/ Evelin</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Kim C</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3rd week</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry
-(Grafton)</t>
-        </is>
-      </c>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
@@ -1471,10 +1467,14 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OUTPOST NATURAL FOODS, MEQUON</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1486,53 +1486,47 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>FESTIVAL #2735, MAUSTON - LIFO</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -1544,10 +1538,14 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7590 W MEQUON RD</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1559,59 +1557,51 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Early office meet</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>750 N UNION ST</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
@@ -1620,10 +1610,14 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/do2xmdVUL8z</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1635,53 +1629,53 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/8fV8TwF5DKH2</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>w/ DJ
-Aurora @ 7:30</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -1692,8 +1686,16 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
@@ -1703,54 +1705,50 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Early office meet</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Katie C</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
@@ -1759,21 +1757,9 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
@@ -1782,7 +1768,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1793,43 +1779,51 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
@@ -1838,16 +1832,8 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
@@ -1857,24 +1843,23 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -1885,31 +1870,31 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
@@ -1918,21 +1903,13 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alyssa H</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>@ Store, Trainer</t>
-        </is>
-      </c>
+          <t>6:00 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
@@ -1941,7 +1918,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1952,40 +1929,47 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>@ Store,
-Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
     </row>
@@ -1994,34 +1978,38 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>@ Store, work w/ Alyssa H</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2032,23 +2020,36 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Nagui</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver 1/2
+Red Van</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
@@ -2057,53 +2058,78 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Driver 1/2
+Red Van</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>Joseph</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>7:30 AM START</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
     </row>
@@ -2113,25 +2139,37 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1108, LOMIRA</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2140,17 +2178,34 @@
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
     </row>
@@ -2160,32 +2215,48 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>375 EAST AVENUE, SUITE 1</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1041, TWO RIVERS</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
     </row>
@@ -2197,33 +2268,37 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>https://goo.gl/maps/HZvTzhm2zfv</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>DISCOUNT LIQUOR INC, MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>5300 MEMORIAL DRIVE, SUITE 103</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -2234,35 +2309,43 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5031 W OKLAHOMA AVE</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/7zzPH72TWHs</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -2272,18 +2355,26 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OUTPOST NATURAL FOODS, MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/hfa57ctXcvNrGJ4NA</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2291,19 +2382,31 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Milwaukee Office</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Help at Pick n Save after if needed</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -2316,31 +2419,47 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>100 E CAPITOL DR</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>PICK #308, WAUKESHA - SUNSET EAST</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Kim G</t>
+          <t>PICK #857 +RX, ST FRANCIS - WHITNALL</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -2351,58 +2470,49 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/n94xpFtHzvE2</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>220 E SUNSET DR</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>4698 S WHITNALL</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Start at 
-Pick n Save,
-Equip</t>
-        </is>
-      </c>
+          <t>PICK #431, FRANKLIN -
+S LOVERS LANE RD</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
     </row>
@@ -2412,49 +2522,52 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Milwaukee Office</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/jn6VPu5yR4C2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/fxhnBtwx5642</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Start at 
-Pick n Save</t>
-        </is>
-      </c>
+          <t>7780 S LOVERS LANE ROAD</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2463,48 +2576,48 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>SET UP ON REG #5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/vq4QCMAV1rj</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
@@ -2514,40 +2627,52 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Kim G</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>SET UP ON REG CLOSEST TOWARDS RESTROOMS</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -2557,25 +2682,41 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -2584,7 +2725,7 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>SMALL RESETS-REMAPPED</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
@@ -2596,24 +2737,36 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -2621,11 +2774,7 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -2635,45 +2784,57 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6:30 AM MEET WATERTOWN PLANK</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4:45 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>PICK #366 +RX, HALES CORNERS</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
     </row>
@@ -2686,26 +2847,50 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>5800 S 108TH ST</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
@@ -2721,26 +2906,50 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Kim G</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/zX1XvNMo8SU2</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -2753,31 +2962,55 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>5:00 AM START</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>EAST SIDE MART, JACKSON</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Until noon</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #238, WAUPUN</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -2788,44 +3021,52 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>N168 W1940 MAIN ST</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>100 GATEWAY DR</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
     </row>
@@ -2835,37 +3076,49 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>OUTPOST NATURAL FOODS, WAUWATOSA</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/hgxGLx2srCs</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/aYPh6GWi7S4ZA8VX6</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -2878,19 +3131,35 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>7000 W STATE ST</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Until 11:00</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
@@ -2899,12 +3168,12 @@
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
@@ -2917,54 +3186,69 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/9Apjjj8M6672</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
         <is>
           <t>Driver,
-Camry,
-Equip</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>3rd week</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
     </row>
@@ -2974,48 +3258,64 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>**Help at Metcalfe after**</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Kim C</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>3rd week</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -3028,29 +3328,65 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Michelle S</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr"/>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
     </row>
@@ -3059,42 +3395,68 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Michelle S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Driver, 
+Sante Fe</t>
+        </is>
+      </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Michelle S</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -3110,38 +3472,62 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -3157,45 +3543,57 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3204,16 +3602,8 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -3224,25 +3614,25 @@
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3251,16 +3641,8 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3275,21 +3657,9 @@
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3303,32 +3673,28 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>COURTESY MEET</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3342,32 +3708,32 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>5:30 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Milwaukee Office</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
     </row>
@@ -3377,41 +3743,36 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1012, CUDAHY</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Kim G</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
     </row>
@@ -3421,40 +3782,32 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>5900 S LAKE DRIVE</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
     </row>
@@ -3464,41 +3817,32 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>METCALFE'S MARKET #560, WAUWATOSA</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1122, HUBERTUS</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/gJd9TeY5Upy</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
     </row>
@@ -3508,15 +3852,15 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>6700 W STATE ST</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1303 HIGHWAY 175</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -3527,21 +3871,9 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -3551,40 +3883,40 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/hbUxBiCRdt72</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/4Vge5Fbx2R4sNroN8</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
     </row>
@@ -3620,25 +3952,26 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Kim G</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -3659,21 +3992,25 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -3684,11 +4021,7 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>5:15 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
@@ -3698,24 +4031,20 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
         <is>
           <t>3)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>1st Financial, work w/ Evelin</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
@@ -3727,11 +4056,7 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -3741,16 +4066,8 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3766,11 +4083,7 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -3780,21 +4093,9 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -3809,11 +4110,7 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #145, KEWASKUM</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -3823,25 +4120,16 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>@ Store,
-Trainer</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -3853,11 +4141,7 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>890 FOND DU LAC AVE</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -3867,24 +4151,16 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -3896,11 +4172,7 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/iZr1X51Jf9U2</t>
-        </is>
-      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -3910,24 +4182,16 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Katie C</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>@ Store, work w/ Marcia, Until 12:45</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
@@ -3949,24 +4213,16 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>CONDON OIL #230, WAUTOMA</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
@@ -3977,21 +4233,9 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
     </row>
@@ -4000,24 +4244,16 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>W7711 STATE RD 21</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
@@ -4028,16 +4264,8 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
@@ -4052,7 +4280,11 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/Todd4ZTFuYD2</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -4063,21 +4295,9 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Alyssa H</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>@ Store, Trainer</t>
-        </is>
-      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
     </row>
@@ -4091,7 +4311,11 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
@@ -4102,21 +4326,9 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Katie C</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>@ Store, 1st Pig, work w/ Alyssa H</t>
-        </is>
-      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
     </row>
@@ -4130,7 +4342,11 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -4141,21 +4357,9 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
     </row>
@@ -4169,7 +4373,11 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>CONDON OIL #180, REDGRANITE</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -4180,21 +4388,9 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
     </row>
@@ -4208,7 +4404,11 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>900 BANNERMAN ST</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -4219,23 +4419,147 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>@ Store, 2nd Pig, work w/ Marcia</t>
-        </is>
-      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/D4tbL8dtjiM2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>@ Store, Until Noon</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y84"/>
+  <dimension ref="A1:AA80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Apr 7</t>
+          <t>Sun, Apr 14</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 8</t>
+          <t>Mon, Apr 15</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 9</t>
+          <t>Tue, Apr 16</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Apr 10</t>
+          <t>Wed, Apr 17</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Apr 11</t>
+          <t>Thu, Apr 18</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Apr 12</t>
+          <t>Fri, Apr 19</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,9 +467,11 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Apr 13</t>
-        </is>
-      </c>
+          <t>Sat, Apr 20</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -497,6 +499,8 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -524,6 +528,8 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -555,6 +561,8 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -586,6 +594,8 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -617,6 +627,8 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -648,20 +660,22 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5:15 AM MEET BAYSHORE</t>
+          <t>4:15 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -669,7 +683,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -685,7 +699,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET AT THE OFFICE</t>
+          <t>4:45 AM MEET RACINE COURT (HWYY 43 &amp; Y)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -693,22 +707,32 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4:30 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -740,16 +764,26 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #364, MENOMONEE FALLS</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -787,22 +821,32 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>PICK #880 +RX, GLENDALE-SILVER SPRING</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N81 W15182 APPLETON AVE</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FESTIVAL #2702, MANITOWOC - LIFO</t>
+          <t>PIGGLY WIGGLY #385, KAUKAUNA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -810,7 +854,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #520 +RX, CHICAGO-BRIDGEPORT</t>
+          <t>MARIANO'S #535 +RX,ORLAND PARK</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -818,8 +862,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #534 +RX, 
-NEW CITY</t>
+          <t>MARIANO'S #536 +FUEL CENTER-RX, WESTMONT</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -827,7 +870,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1174 WALWORTH</t>
+          <t>MARIANO'S #544 +FUEL CENTER-RX, CRYSTAL LAKE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -835,22 +878,32 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>MARIANO'S #532 +RX, GLENVIEW</t>
+          <t>1735 W SILVER SPRING</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>MILLER &amp; SONS SUPERMARKET, VERONA</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/gqjVNncxKSq</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2151 S 42ND ST</t>
+          <t>300 E ANN ST</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -858,7 +911,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3145 S ASHLAND AVE</t>
+          <t>9504 142ND ST</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -866,7 +919,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1500 N CLYBOURN AVE</t>
+          <t>150 W 63RD ST</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -874,7 +927,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>525 KENOSHA ST, SUITE C</t>
+          <t>105 NORTHWEST HWY</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -882,22 +935,32 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2323 CAPITAL DR</t>
+          <t>https://goo.gl/maps/SUc4yjc7BVT2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>210 S MAIN ST</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FROZEN RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ynTuKFekbGQ2</t>
+          <t>https://goo.gl/maps/bhYPnHyrPcz</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -905,7 +968,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/8Wt7uwiJSHJ2</t>
+          <t>https://goo.gl/maps/x3S76RraqQ82</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -913,7 +976,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jSfCth27mhJ2</t>
+          <t>https://goo.gl/maps/9cugGMSRw3F2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -921,7 +984,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/HYXAm9E8G2X4pAUGA</t>
+          <t>https://goo.gl/maps/PTcufZmqU332</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -929,12 +992,18 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ut53mE2zZpL2</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/bBRpVEnzkgivH6R69</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -942,13 +1011,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LIQUOR RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>SET UP ON REG 1 OR 2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -956,234 +1029,298 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #7</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>SET UP ON LAST REG BY STORE DIRECTORS OFFICE</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>SET UP ON REG #2</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEW FROZEN DRS, BUT NO MAJOR PRODUCT CHANGES PER PAUL </t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Katherine, Carlie, and Sue will start at Mariano's</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>Equip</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>@ Store,
-Optima</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Driver,
-Camry</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1195,59 +1332,98 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>3)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Driver,
-Camry</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+Red Van</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1264,72 +1440,84 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>4)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>4:30 AM MEET AT THE OFFICE</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1337,130 +1525,186 @@
           <t>Ian</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van
+Rx</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe,
+Rx</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>5)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe</t>
-        </is>
-      </c>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Kailee</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2nd week</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Kailee</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2nd week</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe,
+Rx</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1469,7 +1713,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1477,61 +1721,85 @@
           <t>Lincoln</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>w/ Carlie</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>7)</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>FESTIVAL #2735, MAUSTON - LIFO</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Kailee</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1540,7 +1808,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1552,12 +1820,12 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1568,42 +1836,65 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry,
+Supv Rx</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>8)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>750 N UNION ST</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1612,74 +1903,83 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>9)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/8fV8TwF5DKH2</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1688,24 +1988,24 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1716,59 +2016,89 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>10)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>Rx</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Xenia</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1779,53 +2109,60 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store,
+Supv Rx</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1838,12 +2175,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1854,49 +2191,59 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1904,21 +2251,17 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>6:00 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1929,49 +2272,51 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>w/ Carlie</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1979,21 +2324,17 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2004,12 +2345,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2020,38 +2361,27 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Driver 1/2
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2059,21 +2389,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2084,12 +2410,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2100,38 +2426,27 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Driver 1/2
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2139,37 +2454,21 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1108, LOMIRA</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2178,36 +2477,21 @@
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Mai</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2215,50 +2499,44 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>375 EAST AVENUE, SUITE 1</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2266,42 +2544,52 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/HZvTzhm2zfv</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #328, FOND DU LAC</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2315,103 +2603,99 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:30 AM START</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>131 UNIVERSITY AVE</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>PICK #368 +RX, BROOKFIELD CAL-CAP</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>https://goo.gl/maps/QmMfhkkrDpNxyhyC8</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2425,44 +2709,35 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PICK #308, WAUKESHA - SUNSET EAST</t>
+          <t>17295 WEST CAPITOL DR</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>PICK #857 +RX, ST FRANCIS - WHITNALL</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>FESTIVAL #2725, MENASHA -LIFO</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Trevor to meet with Michelle 
+@ St Pt Target @ 4:30 AM</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2476,45 +2751,30 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>220 E SUNSET DR</t>
+          <t>https://goo.gl/maps/33rm1Fc6q4o</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4698 S WHITNALL</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>1355 ONEIDA ST</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>PICK #431, FRANKLIN -
-S LOVERS LANE RD</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2522,17 +2782,13 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Milwaukee Office</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jn6VPu5yR4C2</t>
+          <t>SET UP REG #1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2540,36 +2796,38 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fxhnBtwx5642</t>
+          <t>*Crew will start at Marianos - Aurora is 15 min away</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/i2zDN3asp132</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>7780 S LOVERS LANE ROAD</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2577,50 +2835,48 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
+          <t>SMALL RESETS-REMAPPED</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>8:00 AM START</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/vq4QCMAV1rj</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Driver, Gold Camry</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2635,47 +2891,45 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>SET UP ON REG CLOSEST TOWARDS RESTROOMS</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2693,44 +2947,60 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>AURORA RX #1511, 
+DOWNERS GROVE, ILLINOIS</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>Carlie</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>SMALL RESETS-REMAPPED</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr"/>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2748,36 +3018,55 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>3815 HIGHLAND AVE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2795,48 +3084,54 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>https://maps.app.goo.gl/vSZ8KcZ24WBH8NDa9</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>4:45 AM MEET WATERTOWN PLANK</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2854,48 +3149,55 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>*Reminder will probably need to pay for parking at this site!</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>@ Store,
+After Aurora</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr"/>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -2913,48 +3215,38 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Kim G</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>After Aurora</t>
+          <t>Until 12:00</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -2972,48 +3264,46 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Until noon</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>7)</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #238, WAUPUN</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -3031,44 +3321,50 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Until 11:00</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>100 GATEWAY DR</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3086,36 +3382,36 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Xenia</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/aYPh6GWi7S4ZA8VX6</t>
+          <t>Xenia</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>Lashaun</t>
@@ -3124,6 +3420,8 @@
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3141,44 +3439,42 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Until 11:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store </t>
+        </is>
+      </c>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3196,7 +3492,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Jeri</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3205,52 +3501,33 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Jeri</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Courtney</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Driver,
-Altima, Equip</t>
+          <t xml:space="preserve">@ Store </t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3277,47 +3554,37 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr"/>
+          <t>Laurie</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store </t>
+        </is>
+      </c>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3340,55 +3607,42 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Michelle S</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store </t>
+        </is>
+      </c>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3406,7 +3660,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Michelle S</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3415,57 +3669,33 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Nagui</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Driver, 
-Sante Fe</t>
+          <t xml:space="preserve">@ Store </t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Michelle S</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3488,55 +3718,26 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Supv Rx</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3563,32 +3764,12 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -3596,6 +3777,8 @@
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3614,27 +3797,21 @@
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>LEAVE OFFICE @ 4:30 AM</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3654,7 +3831,11 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -3662,6 +3843,8 @@
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3675,21 +3858,21 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>COURTESY MEET</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -3697,6 +3880,8 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3710,23 +3895,19 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>5:30 AM MEET WATERTOWN PLANK</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Milwaukee Office</t>
+          <t>AURORA OUTPATIENT RX #1030, OSHKOSH</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -3736,6 +3917,8 @@
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3749,23 +3932,19 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>AURORA OUTPATIENT RX #1260, WAUWATOSA</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1012, CUDAHY</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Kim G</t>
+          <t>414 DOCTORS COURT SUITE 100</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
@@ -3775,6 +3954,8 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3788,21 +3969,21 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>1055 NORTH MAYFAIR RD SUITE 100</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>5900 S LAKE DRIVE</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/7jsxtRm7nJ82</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -3810,6 +3991,8 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3823,17 +4006,13 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1122, HUBERTUS</t>
+          <t>https://goo.gl/maps/NV3ZZdgjMJXbNG4s7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/gJd9TeY5Upy</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
@@ -3845,6 +4024,8 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -3856,26 +4037,37 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>1303 HIGHWAY 175</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry, Equip</t>
+        </is>
+      </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -3886,29 +4078,25 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/4Vge5Fbx2R4sNroN8</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3919,6 +4107,8 @@
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -3946,6 +4136,8 @@
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -3956,22 +4148,9 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -3986,6 +4165,8 @@
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -3996,21 +4177,13 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t xml:space="preserve">LEAVE OFFICE @ 5:30 AM </t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -4025,6 +4198,8 @@
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -4035,14 +4210,10 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4060,6 +4231,8 @@
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -4071,7 +4244,11 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -4087,6 +4264,8 @@
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -4098,7 +4277,11 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>CONDON OIL #150, KIEL</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
@@ -4114,6 +4297,8 @@
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -4127,7 +4312,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
+          <t>84 E PARK AVE</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4145,6 +4330,8 @@
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -4158,7 +4345,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>https://goo.gl/maps/HE1oXp7RZPP2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4176,6 +4363,8 @@
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -4189,7 +4378,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4207,6 +4396,8 @@
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -4220,7 +4411,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>CONDON OIL #230, WAUTOMA</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4238,6 +4429,8 @@
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -4251,7 +4444,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>W7711 STATE RD 21</t>
+          <t>CONDON OIL #165, CHILTON</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -4269,6 +4462,8 @@
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -4282,7 +4477,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Todd4ZTFuYD2</t>
+          <t>613 N MADISON ST</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -4300,6 +4495,8 @@
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -4313,7 +4510,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>https://goo.gl/maps/idhDxXsWdCT2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -4331,6 +4528,8 @@
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -4342,11 +4541,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -4362,6 +4557,8 @@
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -4372,13 +4569,21 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>CONDON OIL #180, REDGRANITE</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
@@ -4393,6 +4598,8 @@
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -4403,13 +4610,21 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>900 BANNERMAN ST</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>@ Store, Until 11:15</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
@@ -4424,142 +4639,8 @@
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/D4tbL8dtjiM2</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>@ Store, Until Noon</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA80"/>
+  <dimension ref="A1:Y88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Apr 14</t>
+          <t>Sun, Apr 21</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 15</t>
+          <t>Mon, Apr 22</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 16</t>
+          <t>Tue, Apr 23</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Apr 17</t>
+          <t>Wed, Apr 24</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Apr 18</t>
+          <t>Thu, Apr 25</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Apr 19</t>
+          <t>Fri, Apr 26</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,11 +467,9 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Apr 20</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
+          <t>Sat, Apr 27</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -499,8 +497,6 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -528,8 +524,6 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -561,8 +555,6 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -594,8 +586,6 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -627,8 +617,6 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -660,22 +648,24 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>4:30 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4:15 AM MEET WATERTOWN PLANK</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -683,7 +673,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:30 AM START</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -691,7 +681,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t xml:space="preserve">5:30 AM START </t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -699,7 +689,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4:45 AM MEET RACINE COURT (HWYY 43 &amp; Y)</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -707,29 +697,27 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4:30 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>6:00 AM START</t>
@@ -740,7 +728,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -748,7 +736,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -764,24 +752,18 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #364, MENOMONEE FALLS</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -797,7 +779,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>ROTE OIL #6 HUBERTUS</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -805,7 +787,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -813,7 +795,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -821,24 +803,18 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>PICK #880 +RX, GLENDALE-SILVER SPRING</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N81 W15182 APPLETON AVE</t>
+          <t>MILLER &amp; SONS SUPERMARKET, MT HOREB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -846,7 +822,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #385, KAUKAUNA</t>
+          <t>ROTE OIL #03 TWIN LAKES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -854,7 +830,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #535 +RX,ORLAND PARK</t>
+          <t>1306 HWY 175</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -862,7 +838,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #536 +FUEL CENTER-RX, WESTMONT</t>
+          <t>1060 N ROCHESTER ST</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -870,7 +846,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #544 +FUEL CENTER-RX, CRYSTAL LAKE</t>
+          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -878,24 +854,18 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1735 W SILVER SPRING</t>
+          <t>ROTE OIL #14 TREVOR (CITGO)</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>MILLER &amp; SONS SUPERMARKET, VERONA</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/gqjVNncxKSq</t>
+          <t>1845 SPRINGDALE ST</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -903,7 +873,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>300 E ANN ST</t>
+          <t>475 N LAKE AVE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -911,7 +881,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9504 142ND ST</t>
+          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -919,7 +889,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>150 W 63RD ST</t>
+          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -927,7 +897,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>105 NORTHWEST HWY</t>
+          <t>25406 75TH ST</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -935,24 +905,18 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/SUc4yjc7BVT2</t>
+          <t>12617 ANTIOCH RD</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>210 S MAIN ST</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FROZEN RESET-REMAPPED</t>
+          <t>https://goo.gl/maps/zSVBPqJx7dR2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -960,7 +924,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/bhYPnHyrPcz</t>
+          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -968,7 +932,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/x3S76RraqQ82</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -976,7 +940,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/9cugGMSRw3F2</t>
+          <t xml:space="preserve">TO FOLLOW   </t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -984,7 +948,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/PTcufZmqU332</t>
+          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -992,18 +956,12 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/bBRpVEnzkgivH6R69</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1013,7 +971,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LIQUOR RESET-REMAPPED</t>
+          <t xml:space="preserve">TO FOLLOW   </t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1021,7 +979,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG 1 OR 2</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1029,7 +987,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1037,18 +995,20 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>SET UP ON LAST REG BY STORE DIRECTORS OFFICE</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1058,66 +1018,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ROTE OIL #7 MILWAUKEE</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Katherine, Carlie, and Sue will start at Mariano's</t>
+          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #13 TREVOR (BP)</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1127,86 +1077,52 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #04 GENOA CITY</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>5931 N 91ST ST</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>909 GREENWALD CT</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>12511 ANTIOCH RD</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1216,90 +1132,57 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
+          <t xml:space="preserve">100 ELIZABETH LANE    </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>25555 75TH ST</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1309,100 +1192,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1412,91 +1243,56 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1506,98 +1302,69 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van
-Rx</t>
-        </is>
-      </c>
+          <t>ROTE OIL #8 ELM GROVE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe,
-Rx</t>
-        </is>
-      </c>
+          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1607,7 +1374,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1616,407 +1383,262 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kailee</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2nd week</t>
-        </is>
-      </c>
+          <t>ROTE OIL #05  LAKE GENEVA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>13395 WATERTOWN PLANK RD</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Kailee</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2nd week</t>
-        </is>
-      </c>
+          <t>122 ARROWHEAD DR</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>Driver,
-Sante Fe,
-Rx</t>
+Camry</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
+      <c r="Y21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>300 PELLER RD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>w/ Carlie</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Kailee</t>
-        </is>
-      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ROTE OIL #09 GREENFIELD</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2026,53 +1648,23 @@
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1360 PLEASANT PRAIRIE</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -2081,88 +1673,49 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Xenia</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Driver, Altima</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>12345 W LAYTON AVE</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1263 MENOMONEE FALLS</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>12500 AURORA DR,  SUITE 1000</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -2173,77 +1726,35 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>N84 W16889 MENOMONEE AVE, STE 140</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/cBS6XeGsHAkpmwWFA</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -2254,69 +1765,31 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>w/ Carlie</t>
-        </is>
-      </c>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://maps.app.goo.gl/oLhxTANtiQDoDPgy5</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -2324,64 +1797,58 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4:30 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Camry available, Equip</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2389,54 +1856,46 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -2445,8 +1904,6 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2454,44 +1911,46 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1150, KENOSHA</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2499,28 +1958,24 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #387, WINNECONNE</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>10400 75TH ST</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2529,14 +1984,12 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2544,37 +1997,29 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>910 E MAIN ST</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/K5ZSZyLo7jH2</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -2582,14 +2027,12 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #328, FOND DU LAC</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2597,37 +2040,33 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/yDNLLcepRYT2</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>5:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ENTER BY URGENT CARE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -2635,14 +2074,12 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>131 UNIVERSITY AVE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2656,31 +2093,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PICK #368 +RX, BROOKFIELD CAL-CAP</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>PICK #862 +RX, OAK CREEK - MEGA MALL</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -2688,40 +2113,64 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/QmMfhkkrDpNxyhyC8</t>
+          <t>FESTIVAL #2710, MT PLEASANT - LIFO</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17295 WEST CAPITOL DR</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>FESTIVAL #2725, MENASHA -LIFO</t>
+          <t>8770 S HOWELL AVE</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -2729,162 +2178,195 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Trevor to meet with Michelle 
-@ St Pt Target @ 4:30 AM</t>
+          <t>5740 WASHINGTON AVE</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima,
+Trainer</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/33rm1Fc6q4o</t>
+          <t>AURORA OUTPATIENT RX #1178 LAKE GENEVA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1355 ONEIDA ST</t>
+          <t>https://goo.gl/maps/whvAchGPZWU2</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/PRSb1wjmEbn</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Work w/ Carlie</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SET UP REG #1</t>
+          <t>146 E GENEVA SQ</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>*Crew will start at Marianos - Aurora is 15 min away</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/i2zDN3asp132</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SMALL RESETS-REMAPPED</t>
+          <t>https://goo.gl/maps/7Ady9a9f1nnktk6MA</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>8:00 AM START</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Driver, Gold Camry</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2894,50 +2376,56 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr"/>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>@ Store, Until 12:00</t>
+        </is>
+      </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
@@ -2952,64 +2440,69 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>Driver,
+Sante Fe, Equip</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>AURORA RX #1511, 
-DOWNERS GROVE, ILLINOIS</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Driver,
-Optima</t>
+          <t>Until 12:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Xenia</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Work w/ Carlie</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
@@ -3018,7 +2511,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3026,47 +2519,36 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3815 HIGHLAND AVE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -3077,61 +2559,47 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/vSZ8KcZ24WBH8NDa9</t>
+          <t>PICK #178 +RX, MADISON-SHOPKO DR</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Until 11:00</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -3142,62 +2610,52 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>*Reminder will probably need to pay for parking at this site!</t>
+          <t>2502 SHOPKO DRIVE</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>@ Store,
-After Aurora</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Nagui</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Red Van</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -3208,45 +2666,56 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>5:15 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/mzSRZ7wKTvq</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>Lincoln</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -3257,53 +2726,52 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>RESET-</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -3314,57 +2782,47 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3375,53 +2833,59 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Xenia</t>
+          <t>FESTIVAL #2708, OSHKOSH - LIFO</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Xenia</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3432,49 +2896,55 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>2415 WESTOWNE AVE</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store </t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3485,49 +2955,55 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/SYenrFArvdC2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Courtney</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store </t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3538,43 +3014,39 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Josie</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>LIQUOR RESET-REMAPPED</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store </t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -3583,8 +3055,6 @@
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3595,44 +3065,46 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
+          <t>*Carlie to drop off the Optima at the office</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>@ Store,
 Rx</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store </t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -3641,8 +3113,6 @@
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3653,49 +3123,47 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Nagui</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store </t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3708,36 +3176,57 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>@ Store,
-Supv Rx</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>MODAS / WINTAKES</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3750,35 +3239,63 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>*drop Optima</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry,
+Rx</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
           <t>Victoria</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SCHIERL #59, WESTON - CTY RD J</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3789,29 +3306,48 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Xenia</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>LEAVE OFFICE @ 4:30 AM</t>
-        </is>
-      </c>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>6606 COUNTY RD J</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3822,29 +3358,47 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/sr7sZYxNPHacNdrP8</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3855,22 +3409,38 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
@@ -3880,8 +3450,6 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3892,33 +3460,59 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1030, OSHKOSH</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3929,33 +3523,59 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1260, WAUWATOSA</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>414 DOCTORS COURT SUITE 100</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3966,33 +3586,63 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1055 NORTH MAYFAIR RD SUITE 100</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/7jsxtRm7nJ82</t>
+          <t>FESTIVAL #2716, APPLETON - DARBOY - LIFO</t>
         </is>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jacqui</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -4003,29 +3653,63 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/NV3ZZdgjMJXbNG4s7</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>Courtney</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>W3195 VAN ROY RD</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Driver, Gold Camry</t>
+        </is>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -4036,38 +3720,63 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry, Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/57s41PSXiLJ2</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>meet Michelle 6:15 AM @ Point Target</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -4080,26 +3789,42 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESET-REMAPPED </t>
+        </is>
+      </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -4107,8 +3832,6 @@
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -4119,9 +3842,21 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -4136,8 +3871,6 @@
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -4148,25 +3881,51 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>@ Store, Until 11:30</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -4177,29 +3936,51 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEAVE OFFICE @ 5:30 AM </t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>@ Store, Until 2</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>4:45 AM MEET AT BAYSHORE</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -4211,28 +3992,39 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>6:30 AM START</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -4244,28 +4036,43 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>MODAS</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>TOB ONLY</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -4279,26 +4086,40 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>CONDON OIL #150, KIEL</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>ONEIDA #2022 ONE STOP E &amp; EE, DEPERE</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>work w/ Lincoln</t>
+        </is>
+      </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -4312,17 +4133,29 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>84 E PARK AVE</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>790 COUNTY RD EE</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -4330,8 +4163,6 @@
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -4343,28 +4174,38 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/HE1oXp7RZPP2</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/VLR8RdvzGgF2</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -4376,19 +4217,27 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW  </t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -4396,8 +4245,6 @@
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -4409,19 +4256,27 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>MODAS</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -4429,8 +4284,6 @@
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -4442,28 +4295,38 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>CONDON OIL #165, CHILTON</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>ONEIDA #2021 ONE STOP 54, ONEIDA</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Xenia</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>work w/ Lincoln</t>
+        </is>
+      </c>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -4475,28 +4338,38 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>613 N MADISON ST</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>W180 HWY 54</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -4508,28 +4381,38 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/idhDxXsWdCT2</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/kMzccLLaPd22</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -4545,7 +4428,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW  </t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
@@ -4557,8 +4444,6 @@
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -4569,24 +4454,16 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>MODAS</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
@@ -4598,8 +4475,6 @@
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -4610,24 +4485,16 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>@ Store, Until 11:15</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ONEIDA #2024 TRAVEL CENTER, PULASKI</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
@@ -4639,8 +4506,287 @@
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>5939 OLD 29 DRIVE</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/P7gcbpqmHRw</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1st Modas</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y88"/>
+  <dimension ref="A1:Y72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Apr 21</t>
+          <t>Sun, Apr 28</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 22</t>
+          <t>Mon, Apr 29</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 23</t>
+          <t>Tue, Apr 30</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Apr 24</t>
+          <t>Wed, May 1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Apr 25</t>
+          <t>Thu, May 2</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Apr 26</t>
+          <t>Fri, May 3</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Apr 27</t>
+          <t>Sat, May 4</t>
         </is>
       </c>
     </row>
@@ -651,11 +651,7 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4:30 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -665,7 +661,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t>4:30 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -673,7 +669,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5:30 AM START</t>
+          <t>5:45 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -681,7 +677,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5:30 AM START </t>
+          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -689,7 +685,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -697,7 +693,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t>5:15 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -706,18 +702,10 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>6:00 AM START</t>
@@ -728,7 +716,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -736,7 +724,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -761,11 +749,7 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -779,7 +763,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ROTE OIL #6 HUBERTUS</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -787,7 +771,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -795,7 +779,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -803,7 +787,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -812,17 +796,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MILLER &amp; SONS SUPERMARKET, MT HOREB</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ROTE OIL #03 TWIN LAKES</t>
+          <t>WEBSTER'S MARKETPLACE, RIPON</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -830,7 +810,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1306 HWY 175</t>
+          <t>FESTIVAL #2696, HARTFORD - LIFO</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -838,7 +818,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1060 N ROCHESTER ST</t>
+          <t>MARIANO'S #503, CHICAGO - LAKESHORE EAST</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -846,7 +826,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
+          <t>MARIANO'S #510 +RX, HARWOOD HEIGHTS</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -854,7 +834,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>ROTE OIL #14 TREVOR (CITGO)</t>
+          <t>PICK #343, PLYMOUTH</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -863,17 +843,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1845 SPRINGDALE ST</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>475 N LAKE AVE</t>
+          <t>1188 W FOND DU LAC STREET</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -881,7 +857,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
+          <t>1275 BELL AVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -889,7 +865,8 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
+          <t>333 EAST BENTON PL, 
+SUITE 206</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -897,7 +874,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>25406 75TH ST</t>
+          <t>7401 WEST LAWRENCE AVENUE</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -905,7 +882,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>12617 ANTIOCH RD</t>
+          <t>2643 EASTERN AVE</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -914,17 +891,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/zSVBPqJx7dR2</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
+          <t>https://goo.gl/maps/EWZS96J1G93UVQgi7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -932,7 +905,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>https://goo.gl/maps/PUKTG8ru54xUWw7d9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -940,7 +913,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>https://goo.gl/maps/Gwa8pwADYxr</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -948,7 +921,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
+          <t>https://goo.gl/maps/Nv5frfdAopr</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -956,7 +929,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
+          <t>https://goo.gl/maps/uM51wiLfFCA2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -971,23 +944,19 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>SMALL RESET-REMAPPED</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>NEED TO PAY FOR PARKING AT THIS SITE!</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -995,129 +964,143 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ROTE OIL #7 MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>ROTE OIL #13 TREVOR (BP)</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ROTE OIL #04 GENOA CITY</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5931 N 91ST ST</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>909 GREENWALD CT</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>12511 ANTIOCH RD</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -1125,544 +1108,712 @@
       <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>3)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>*After Aurora</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>Driver,
 Red Van</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100 ELIZABETH LANE    </t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>25555 75TH ST</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL </t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ROTE OIL #8 ELM GROVE</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Driver,
-Altima</t>
+          <t>After Aurora</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>7)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ROTE OIL #05  LAKE GENEVA</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13395 WATERTOWN PLANK RD</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>122 ARROWHEAD DR</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>8)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>300 PELLER RD</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>@ Store,
+Help Kim</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>9)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:15</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>10)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:15</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ROTE OIL #09 GREENFIELD</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1360 PLEASANT PRAIRIE</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:15</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
@@ -1673,47 +1824,79 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Driver, Altima</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12345 W LAYTON AVE</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1263 MENOMONEE FALLS</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>12500 AURORA DR,  SUITE 1000</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:15</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
@@ -1722,36 +1905,72 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>N84 W16889 MENOMONEE AVE, STE 140</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/cBS6XeGsHAkpmwWFA</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -1761,29 +1980,69 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/oLhxTANtiQDoDPgy5</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -1796,57 +2055,77 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4:30 AM MEET WATERTOWN PLANK</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Camry available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>5:15 AM MEET BAYSHORE</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
@@ -1855,52 +2134,65 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t xml:space="preserve">15) </t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -1910,44 +2202,52 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1150, KENOSHA</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16) </t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -1958,11 +2258,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #387, WINNECONNE</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1972,19 +2268,33 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>10400 75TH ST</t>
+          <t>6:30 AM RACINE COURT 
+(HWY 43 &amp; Y)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17) </t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>6:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>AURORA OUTPATIENT RX #1227, PLYMOUTH</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -1997,37 +2307,45 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>910 E MAIN ST</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5:15 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/K5ZSZyLo7jH2</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>2600 KILEY WAY, SUITE 100</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -2042,7 +2360,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/yDNLLcepRYT2</t>
+          <t>5:30 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2050,7 +2368,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2058,23 +2376,19 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ENTER BY URGENT CARE</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/oK3no3iSD5kXaRa59</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -2087,35 +2401,35 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>KANSASVILLE CITGO QUICK MART</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>PICK #862 +RX, OAK CREEK - MEGA MALL</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>FESTIVAL #2710, MT PLEASANT - LIFO</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -2125,63 +2439,53 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>AURORA OUTPATIENT RX #1102, HARTFORD</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>23010 DURAND AVE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>8770 S HOWELL AVE</t>
+          <t>5:30 AM REQUIRED MEET AT GARFIELD AVE PICK N SAVE</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>5740 WASHINGTON AVE</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
     </row>
@@ -2190,40 +2494,26 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima,
-Trainer</t>
-        </is>
-      </c>
+          <t>KOHN'S FILLING STATION, KEWASKUM</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1178 LAKE GENEVA</t>
+          <t>1640 E SUMNER ST, SUITE 100</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>https://goo.gl/maps/QZs8ZSjv9eL2</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -2231,15 +2521,20 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/whvAchGPZWU2</t>
+          <t>Pick n Save address is:
+1100 E Garfield Ave</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/PRSb1wjmEbn</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -2251,41 +2546,54 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Work w/ Carlie</t>
-        </is>
-      </c>
+          <t>890 FOND DU LAC AVE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>146 E GENEVA SQ</t>
+          <t>https://goo.gl/maps/umuyQZyC8FT2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>5:45 AM START</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2294,61 +2602,37 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>https://goo.gl/maps/CJnRNDyortw</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/7Ady9a9f1nnktk6MA</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
     </row>
@@ -2357,57 +2641,49 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t xml:space="preserve">TO FOLLOW </t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t>TWIN LAKES CITGO, TWIN LAKES</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>ASCENSION IP CSMM COLUMBIA ST MARY'S WOMEN'S MEDICAL CENTER</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:00</t>
-        </is>
-      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
     </row>
@@ -2416,67 +2692,38 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>410 N LAKE AVE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>2323 N LAKE DR</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
@@ -2488,62 +2735,38 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Xenia</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Work w/ Carlie</t>
-        </is>
-      </c>
+          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>https://goo.gl/maps/k9s2GwpMbH32</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>https://goo.gl/maps/86sUJVyjHnUKr7tv8</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W42" t="inlineStr"/>
@@ -2556,45 +2779,37 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>259 N FOND DU LAC AVE</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>6:15 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>PICK #178 +RX, MADISON-SHOPKO DR</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+          <t>In order for everyone to get to the site efficiently and avoid anyone</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>PICK #416, WAUWATOSA - WALNUT</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -2607,53 +2822,53 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2502 SHOPKO DRIVE</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>getting confused on where to go, all must use the meet above</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>1717 N MAYFAIR RD</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
     </row>
@@ -2669,51 +2884,34 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5:15 AM MEET WATERTOWN PLANK</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/mzSRZ7wKTvq</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/96AWc1YH6do</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
     </row>
@@ -2722,51 +2920,42 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>AURORA OUTPATIENT RX #1750 ELKHORN</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>RESET-</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -2778,14 +2967,27 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>201 E MORRISSEY DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -2796,30 +2998,22 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -2836,54 +3030,46 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>FESTIVAL #2708, OSHKOSH - LIFO</t>
+          <t>https://goo.gl/maps/xYN7FT5gMzQk78dv6</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>5:15 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
     </row>
@@ -2897,52 +3083,49 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2415 WESTOWNE AVE</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Altima</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr"/>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
     </row>
@@ -2952,53 +3135,62 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>6:30 AM MEET OFFICE</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/SYenrFArvdC2</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Optima</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
@@ -3011,48 +3203,56 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>LIQUOR RESET-REMAPPED</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>CONDON OIL #120, PRINCETON</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Garfield meet too!</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -3062,54 +3262,51 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>*Carlie to drop off the Optima at the office</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>811 OLD GREEN LAKE RD</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>Until 12:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -3120,45 +3317,49 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>6:30 AM MEET OFFICE</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>https://maps.app.goo.gl/b9UWz2Uc4DF9epFR8</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
@@ -3171,60 +3372,56 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>141 MAIN ST</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>MODAS / WINTAKES</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Until 10:00</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3234,66 +3431,48 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>*drop Optima</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>CONDON OIL #220, GREEN LAKE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
         <is>
           <t>8)</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry,
-Rx</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>SCHIERL #59, WESTON - CTY RD J</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3303,34 +3482,25 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>APPROX 10:00/11:00 AM START</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Xenia</t>
+          <t>514 MILL ST</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -3339,13 +3509,21 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>6606 COUNTY RD J</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3355,48 +3533,52 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>N6485 COUNTY RD F</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://maps.app.goo.gl/9KFU2mUvQ1KBEVvg9</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Milwaukee Office</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/sr7sZYxNPHacNdrP8</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3406,48 +3588,48 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>RON'S MARKET, HELENVILLE</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3457,58 +3639,55 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>W3094 HWY 18</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>APPROX 10:00/10:30 AM START</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Jeri</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, 
+PC Box</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>6:30 AM START</t>
-        </is>
-      </c>
+      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -3520,29 +3699,29 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/pyYX7wkpwom</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Courtney</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -3552,26 +3731,22 @@
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store  </t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -3586,54 +3761,44 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>CONDON OIL #195, THERESA</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Optima
+Help Michelle,
+Take DC5's</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>FESTIVAL #2716, APPLETON - DARBOY - LIFO</t>
-        </is>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Jacqui</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -3649,63 +3814,52 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima, Equip</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Courtney</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>213 N MILWAUKEE</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>W3195 VAN ROY RD</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>Driver, Gold Camry</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
@@ -3716,63 +3870,47 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/dBrycqMgUwF2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/57s41PSXiLJ2</t>
-        </is>
-      </c>
+      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>meet Michelle 6:15 AM @ Point Target</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X63" t="inlineStr"/>
@@ -3787,44 +3925,20 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESET-REMAPPED </t>
-        </is>
-      </c>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -3844,22 +3958,27 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Marcia</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Optima, Equip</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
@@ -3883,44 +4002,28 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>@ Store, Until 11:30</t>
-        </is>
-      </c>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W66" t="inlineStr"/>
@@ -3936,46 +4039,22 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>@ Store, Until 2</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>4:45 AM MEET AT BAYSHORE</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W67" t="inlineStr"/>
@@ -3996,32 +4075,19 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>6:30 AM START</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1017, WAUWATOSA</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -4040,36 +4106,19 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>MODAS</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>TOB ONLY</t>
-        </is>
-      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>1220 DEWEY AVENUE</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -4084,39 +4133,23 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>ONEIDA #2022 ONE STOP E &amp; EE, DEPERE</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>work w/ Lincoln</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/9FX8iZxiZbN2</t>
+        </is>
+      </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -4131,31 +4164,15 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>790 COUNTY RD EE</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -4178,615 +4195,30 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/VLR8RdvzGgF2</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW  </t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>MODAS</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>ONEIDA #2021 ONE STOP 54, ONEIDA</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Xenia</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>work w/ Lincoln</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>W180 HWY 54</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/kMzccLLaPd22</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW  </t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>MODAS</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>ONEIDA #2024 TRAVEL CENTER, PULASKI</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>5939 OLD 29 DRIVE</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/P7gcbpqmHRw</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>1st Modas</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -3559,7 +3559,7 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Milwaukee Office</t>
+          <t>Madison Office</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y72"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Apr 28</t>
+          <t>Sun, May 5</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 29</t>
+          <t>Mon, May 6</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 30</t>
+          <t>Tue, May 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 1</t>
+          <t>Wed, May 8</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 2</t>
+          <t>Thu, May 9</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 3</t>
+          <t>Fri, May 10</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, May 4</t>
+          <t>Sat, May 11</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET WATERTOWN PLANK</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -669,7 +669,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5:45 AM MEET WATERTOWN PLANK</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -677,7 +677,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -685,7 +685,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:15 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -693,7 +693,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5:15 AM MEET BAYSHORE</t>
+          <t>THEY NOW HAVE SIGNS UP NO STREET PARKING</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -716,7 +716,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -740,7 +740,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>11:30 REQUIRED MEEET AT MEN FALLS PICK N SAVE</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -755,7 +755,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>ASCENSION IP CSMO COLUMBIA ST MARY'S HOSP OZAUKEE CAMPUS, MEQUON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -763,7 +763,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -787,7 +787,8 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>ADDRESS TO THE MEET:
+N77 W14435 APPLETON AVE, MENOMONEE FALLS</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -802,7 +803,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WEBSTER'S MARKETPLACE, RIPON</t>
+          <t>13111 N PORT WASHINGTON RD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -810,7 +811,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FESTIVAL #2696, HARTFORD - LIFO</t>
+          <t>MARIANO'S #515 +RX, CHICAGO, RAVENSWOOD</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -818,7 +819,8 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #503, CHICAGO - LAKESHORE EAST</t>
+          <t>MARIANO'S #541 +FC-RX, 
+DES PLAINES</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -826,7 +828,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #510 +RX, HARWOOD HEIGHTS</t>
+          <t>MARIANO'S #523 +RX, GURNEE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -834,7 +836,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>PICK #343, PLYMOUTH</t>
+          <t>12:00 PM START</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -849,7 +851,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1188 W FOND DU LAC STREET</t>
+          <t>https://goo.gl/maps/h68MdySxd6QHKPLu5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -857,7 +859,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1275 BELL AVE</t>
+          <t>1800 WEST LAWRENCE AVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -865,8 +867,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>333 EAST BENTON PL, 
-SUITE 206</t>
+          <t>10 E GOLF RD</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -874,7 +875,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>7401 WEST LAWRENCE AVENUE</t>
+          <t>6655 GRAND AVE</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -882,7 +883,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2643 EASTERN AVE</t>
+          <t>MODAS</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -897,7 +898,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/EWZS96J1G93UVQgi7</t>
+          <t>Need 2 supvs here and for each to bring a box</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -905,7 +906,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/PUKTG8ru54xUWw7d9</t>
+          <t>https://goo.gl/maps/fhp2WWuMFCQ2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -913,7 +914,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Gwa8pwADYxr</t>
+          <t>https://goo.gl/maps/igRLR2wEyh22</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -921,7 +922,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Nv5frfdAopr</t>
+          <t>https://goo.gl/maps/SV1CeAGfq1s</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -929,7 +930,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/uM51wiLfFCA2</t>
+          <t>AURORA OUTPATIENT RX #1119, MENOM FALLS</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -942,21 +943,21 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SMALL RESET-REMAPPED</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SET UP ON REG #7</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>NEED TO PAY FOR PARKING AT THIS SITE!</t>
+          <t>SET UP ON REG #3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -964,13 +965,17 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
+          <t>RESET-REMAPPED</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N93 W14575 WHITTAKER WAY </t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
@@ -980,49 +985,45 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/CLqauUgd2u12</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
@@ -1033,48 +1034,35 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1083,24 +1071,20 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>@ Store,
-Sante Fe, Equip</t>
+Equip</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Area tickets are used here, supervisor will need to arrive early to post them.</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -1114,39 +1098,47 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PC Box</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1160,21 +1152,13 @@
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Make sure to bring folders for both sites - *notes* - Items over $1,000 count as tenths - Count big dollar sections 1st for auditing. </t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
@@ -1185,43 +1169,49 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>*After Aurora</t>
+          <t>Driver,
+Sante Fe</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1230,27 +1220,18 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Make sure to tag each location when completed. Try to start large Drawer sections early - they take a lot of time.</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
@@ -1259,48 +1240,30 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1312,24 +1275,15 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Meet in order to avoid parking issues at the location</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1341,50 +1295,33 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1393,26 +1330,18 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>Only Milwwaukee crew will be at this meet up</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
@@ -1421,78 +1350,62 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Driver,
 Camry</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
@@ -1501,45 +1414,42 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1548,22 +1458,32 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Rx</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
@@ -1572,50 +1492,41 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>@ Store,
-Help Kim</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1222, CEDAR GROVE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1624,28 +1535,25 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>@ Store, Until 1:15</t>
+          <t>Driver,
+Optima</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -1656,46 +1564,34 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>313 SOUTH MAIN ST</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1707,28 +1603,25 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>@ Store, Until 1:15</t>
+          <t>Driver,
+Altima</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -1739,46 +1632,40 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/Z3osjsSq666QtkPNA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Red Van,
+Rx</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -1790,30 +1677,22 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:15</t>
-        </is>
-      </c>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
@@ -1822,30 +1701,22 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>PARK ON STREET</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1856,12 +1727,12 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -1873,7 +1744,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -1884,19 +1755,15 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:15</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
@@ -1905,30 +1772,18 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1939,19 +1794,15 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
@@ -1960,7 +1811,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -1969,8 +1820,16 @@
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -1982,28 +1841,28 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2014,12 +1873,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2035,17 +1894,26 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Supv Rx</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -2057,28 +1925,24 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2089,12 +1953,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2103,26 +1967,18 @@
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>5:15 AM MEET BAYSHORE</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -2134,30 +1990,18 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2166,34 +2010,42 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15) </t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>@ Store,
 Rx</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
     </row>
@@ -2202,53 +2054,65 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>16)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16) </t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>Nate</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
     </row>
@@ -2258,46 +2122,68 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>6:30 AM RACINE COURT 
-(HWY 43 &amp; Y)</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17) </t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>Qiana</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1227, PLYMOUTH</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
     </row>
@@ -2307,47 +2193,55 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>9:00 AM START</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5:15 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2600 KILEY WAY, SUITE 100</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -2360,37 +2254,54 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>5:30 AM MEET WATERTOWN PLANK</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>PICK #891 +RX, RACINE - 
+MT PLEASANT - SOUTH</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/oK3no3iSD5kXaRa59</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -2403,33 +2314,45 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>SMOKE WORLD VAPE, TOB &amp; VAPE OUTLET PLUS, RACINE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20)</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>KANSASVILLE CITGO QUICK MART</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2820 S GREEN BAY ROAD</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>5:15 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -2442,50 +2365,34 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>6100 WASHINGTON AVE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1102, HARTFORD</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>23010 DURAND AVE</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>5:30 AM REQUIRED MEET AT GARFIELD AVE PICK N SAVE</t>
+          <t>https://goo.gl/maps/82wgqsh41W62</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
     </row>
@@ -2497,23 +2404,19 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION, KEWASKUM</t>
+          <t>https://goo.gl/maps/cHN9ujzpR19oH6AF9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>1640 E SUMNER ST, SUITE 100</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/QZs8ZSjv9eL2</t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -2521,20 +2424,15 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Pick n Save address is:
-1100 E Garfield Ave</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -2547,17 +2445,13 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>890 FOND DU LAC AVE</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/umuyQZyC8FT2</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2565,35 +2459,22 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>5:45 AM START</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>CONDON OIL #270, POY SIPPI</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2602,37 +2483,66 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/CJnRNDyortw</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van, Equip</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>(7AM - 3PM)</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>ASCENSION ELMBROOK HOSPITAL RX #1104</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>239 MAIN ST</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>C-STORE ONLY</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
     </row>
@@ -2641,48 +2551,60 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW </t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Train w/ Lashaun</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+          <t>PAID VIRTUAL SEMINAR - LEADERSHIP, TEAM-BUILDING</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>TWIN LAKES CITGO, TWIN LAKES</t>
+          <t>19333 W NORTH AVE  SUITE 390</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ASCENSION IP CSMM COLUMBIA ST MARY'S WOMEN'S MEDICAL CENTER</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/Nz84R23bat22</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -2692,30 +2614,42 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>BROOKFIELD OFFICE</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>410 N LAKE AVE</t>
+          <t>https://goo.gl/maps/HnZswssC8QL2</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2323 N LAKE DR</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
@@ -2723,7 +2657,7 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
@@ -2735,10 +2669,14 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2750,26 +2688,40 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/k9s2GwpMbH32</t>
+          <t>GO IN THROUGH EMERGENCY ENTRANCE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/86sUJVyjHnUKr7tv8</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr"/>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>C-STORE ONLY</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
     </row>
@@ -2779,37 +2731,49 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>259 N FOND DU LAC AVE</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6:15 AM OFFICE LEAVE TIME</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>In order for everyone to get to the site efficiently and avoid anyone</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>PICK #416, WAUWATOSA - WALNUT</t>
+          <t>CONDON OIL #135, OMRO</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -2822,42 +2786,37 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima, Equip</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>getting confused on where to go, all must use the meet above</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -2865,7 +2824,7 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1717 N MAYFAIR RD</t>
+          <t>163 E MAIN ST</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
@@ -2881,34 +2840,46 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>ASCENSION ST JOSEPH-MAYFAIR RX #1106, TOSA</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/96AWc1YH6do</t>
+          <t>https://goo.gl/maps/w6KtjB6H4g72</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -2920,44 +2891,48 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1750 ELKHORN</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>201 N MAYFAIR RD</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>SET UP ON REG #5</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -2967,54 +2942,61 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>201 E MORRISSEY DRIVE, SUITE 100</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/efsuGG591Ms</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
     </row>
@@ -3027,47 +3009,52 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xYN7FT5gMzQk78dv6</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>5:15 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>Sante Fe, Bring DC5's, 
+help Michelle</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
@@ -3082,48 +3069,63 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Driver,
-Altima</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Jacqui</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Until 12:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
@@ -3135,64 +3137,51 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>6:30 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Driver,
-Optima</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -3203,56 +3192,45 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>CONDON OIL #120, PRINCETON</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>@ Garfield meet too!</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -3262,49 +3240,45 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>811 OLD GREEN LAKE RD</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Until 12:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
@@ -3317,49 +3291,41 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>6:30 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/b9UWz2Uc4DF9epFR8</t>
+          <t>9:00 AM START</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr"/>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
@@ -3372,56 +3338,28 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>141 MAIN ST</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Until 10:00</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3431,25 +3369,18 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>CONDON OIL #220, GREEN LAKE</t>
+          <t>SMOKE WORLD VAPE, 
+OAK CREEK</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -3458,21 +3389,9 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3482,48 +3401,32 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>APPROX 10:00/11:00 AM START</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>514 MILL ST</t>
+          <t>8809 S HOWELL AVE</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>5:15 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3533,25 +3436,17 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>N6485 COUNTY RD F</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/9KFU2mUvQ1KBEVvg9</t>
+          <t>https://goo.gl/maps/1fZ4T4q9WR1Hexjb7</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
@@ -3559,26 +3454,14 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Madison Office</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3588,48 +3471,32 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>RON'S MARKET, HELENVILLE</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>PARK ACROSS THE STREET AT PICK N SAVE AND RIDE TOGETHER STORE HAS SMALL PARKING LOT</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3639,57 +3506,28 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>W3094 HWY 18</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>APPROX 10:00/10:30 AM START</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>@ Store, 
-PC Box</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1433, MT PLEASANT</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
     </row>
@@ -3699,56 +3537,40 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/pyYX7wkpwom</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Courtney</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>13250 WASHINGTON AVE, SUITE 1A0043</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
     </row>
@@ -3762,50 +3584,32 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>CONDON OIL #195, THERESA</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Optima
-Help Michelle,
-Take DC5's</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/hWixpCQuYhJ3PMrB9</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
     </row>
@@ -3814,54 +3618,33 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima, Equip</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>213 N MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
     </row>
@@ -3870,49 +3653,45 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/dBrycqMgUwF2</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -3930,16 +3709,25 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
@@ -3947,279 +3735,6 @@
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima, Equip</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1017, WAUWATOSA</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>1220 DEWEY AVENUE</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/9FX8iZxiZbN2</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:AA66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, May 5</t>
+          <t>Sun, May 12</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, May 6</t>
+          <t>Mon, May 13</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, May 7</t>
+          <t>Tue, May 14</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 8</t>
+          <t>Wed, May 15</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 9</t>
+          <t>Thu, May 16</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 10</t>
+          <t>Fri, May 17</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,9 +467,11 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, May 11</t>
-        </is>
-      </c>
+          <t>Sat, May 18</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -497,6 +499,8 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -524,6 +528,8 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -555,6 +561,8 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -586,6 +594,8 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -617,6 +627,8 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -648,10 +660,16 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MOTHER'S DAY</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -661,7 +679,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>4:45 AM REQUIRED MEET AT CAPITOL DR PICK N SAVE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -669,7 +687,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -677,7 +695,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -685,7 +703,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -693,22 +711,33 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>THEY NOW HAVE SIGNS UP NO STREET PARKING</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>ADDRESS TO THE MEET:
+5700 W CAPITOL DR, MILW</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -732,7 +761,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -740,22 +769,32 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>11:30 REQUIRED MEEET AT MEN FALLS PICK N SAVE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASCENSION IP CSMO COLUMBIA ST MARY'S HOSP OZAUKEE CAMPUS, MEQUON</t>
+          <t>ENTER THRU MATERNITY (3RD LEVEL) VISITOR ENTRANCE.  RX IS IN THE LOBBY</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -779,7 +818,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>METRO #371 +RX, MILWAUKEE</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -787,23 +826,32 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>ADDRESS TO THE MEET:
-N77 W14435 APPLETON AVE, MENOMONEE FALLS</t>
+          <t>PICK #374, PEWAUKEE - CAPITOL DR</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #200, MEQUON</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13111 N PORT WASHINGTON RD</t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -811,7 +859,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #515 +RX, CHICAGO, RAVENSWOOD</t>
+          <t>MARIANO'S #524 +RX, NORTHFIELD</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -819,8 +867,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #541 +FC-RX, 
-DES PLAINES</t>
+          <t>MARIANO'S #537 +RX, NAPERVILLE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -828,7 +875,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #523 +RX, GURNEE</t>
+          <t>1123 N VAN BUREN STREET</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -836,12 +883,18 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>12:00 PM START</t>
+          <t>1405 CAPITOL DRIVE</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6111 W MEQUON RD</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -851,7 +904,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/h68MdySxd6QHKPLu5</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -859,7 +912,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1800 WEST LAWRENCE AVE</t>
+          <t>1822 WILLOW RD</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -867,7 +920,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10 E GOLF RD</t>
+          <t>1300 S NAPER BLVD</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -875,7 +928,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>6655 GRAND AVE</t>
+          <t>https://goo.gl/maps/P9qm8u7dxgH2</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -883,12 +936,18 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>MODAS</t>
+          <t>https://goo.gl/maps/fM2WtjtDye32</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/vQEGbDwowNJ7UTyo7</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -898,7 +957,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Need 2 supvs here and for each to bring a box</t>
+          <t>ASCENSION ST JOSEPH RX-CHAMBERS #1103, MILW</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -906,7 +965,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fhp2WWuMFCQ2</t>
+          <t>https://goo.gl/maps/jdSWvCFJ2cU2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -914,28 +973,26 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/igRLR2wEyh22</t>
+          <t>https://goo.gl/maps/zEFY7puewEn</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/SV1CeAGfq1s</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1119, MENOM FALLS</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -943,13 +1000,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5000 W CHAMBERS  ROOM 1801</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #7</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -957,89 +1018,109 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #3</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>RESET-REMAPPED</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t xml:space="preserve">N93 W14575 WHITTAKER WAY </t>
+          <t>LIQUOR RESET-REMAPPED</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/gRgCFNfwBUy</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>RESET-REMAPPED</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/CLqauUgd2u12</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t xml:space="preserve">TO FOLLOW   </t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1051,7 +1132,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1060,57 +1141,75 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>@ Store,
-Equip</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Area tickets are used here, supervisor will need to arrive early to post them.</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PC Box</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
@@ -1119,62 +1218,78 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>Driver,
+Optima,
+Rx</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make sure to bring folders for both sites - *notes* - Items over $1,000 count as tenths - Count big dollar sections 1st for auditing. </t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>ASCENSION ST FRANCIS RX #1107, MILWAUKEE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1186,54 +1301,72 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Driver,
-Sante Fe</t>
+Red Van,
+Rx</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>3)</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Make sure to tag each location when completed. Try to start large Drawer sections early - they take a lot of time.</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1241,7 +1374,11 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3237 S 16TH ST    ROOM 121</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
@@ -1251,26 +1388,26 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1280,15 +1417,33 @@
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Meet in order to avoid parking issues at the location</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1296,7 +1451,11 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/ckXW882eGXp</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
@@ -1306,26 +1465,32 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1335,15 +1500,33 @@
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Only Milwwaukee crew will be at this meet up</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1353,7 +1536,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1365,18 +1548,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1388,26 +1567,43 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1429,31 +1625,30 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1463,29 +1658,25 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van,
-Rx</t>
+          <t>Supv Rx</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1495,7 +1686,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1222, CEDAR GROVE</t>
+          <t>ASCENSION RX #1105, FRANKLIN-27TH ST</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1507,57 +1698,59 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1567,7 +1760,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>313 SOUTH MAIN ST</t>
+          <t>10101 S 27TH ST    ROOM 1005</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1579,53 +1772,54 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1635,7 +1829,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Z3osjsSq666QtkPNA</t>
+          <t>https://goo.gl/maps/fQ4V9q61NUS2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1647,54 +1841,54 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1704,7 +1898,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PARK ON STREET</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1716,7 +1910,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1727,24 +1921,24 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -1755,17 +1949,19 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1773,7 +1969,11 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
@@ -1783,7 +1983,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1794,19 +1994,23 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -1822,38 +2026,36 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Until 10:00</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>ASCENSION AMG RAWSON AVE RX #1116, FRANKLIN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
@@ -1862,7 +2064,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1873,12 +2075,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -1889,76 +2091,65 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>@ Store,
-Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:00</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>7400 W RAWSON AVE, SUITE 140</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -1973,17 +2164,23 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr"/>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:00</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -1991,39 +2188,30 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/JDSt1uteEWoVQ3wg8</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2033,7 +2221,7 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -2048,6 +2236,8 @@
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2058,244 +2248,205 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 1:00</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>8:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Justin</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Nagui</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 1:00</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9:00 AM START</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>PICK #846 +RX, WEST ALLIS - 108TH ST</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>PICK #378, RACINE - CALEDONIA</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>PICK #891 +RX, RACINE - 
-MT PLEASANT - SOUTH</t>
+          <t>2625 S 108TH ST</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -2305,96 +2456,111 @@
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, TOB &amp; VAPE OUTLET PLUS, RACINE</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20)</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5111 DOUGLAS AVENUE</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1264, PORT WASHINGTON</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2820 S GREEN BAY ROAD</t>
+          <t>https://goo.gl/maps/BUUQissbQNk</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>5:15 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6100 WASHINGTON AVE</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/b5CYjdz3kAC2</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1475 GRAND AVE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/82wgqsh41W62</t>
-        </is>
-      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>6:15 AM MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2402,42 +2568,52 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/cHN9ujzpR19oH6AF9</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>SMALL RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>https://goo.gl/maps/eMESBveZrkcjkpYJ8</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2449,281 +2625,290 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>CONDON OIL #270, POY SIPPI</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van, Equip</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>(7AM - 3PM)</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>@ Store,
+Equip</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>ASCENSION ELMBROOK HOSPITAL RX #1104</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>239 MAIN ST</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>C-STORE ONLY</t>
-        </is>
-      </c>
+          <t>OPEN PANTRY #493, RACINE</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Train w/ Lashaun</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>PAID VIRTUAL SEMINAR - LEADERSHIP, TEAM-BUILDING</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>19333 W NORTH AVE  SUITE 390</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>After Aurora</t>
+          <t>Until 11:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Nz84R23bat22</t>
+          <t>3441 SPRING ST</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>AURORA OUTPATIENT RX #1230, HOWARDS GROVE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>BROOKFIELD OFFICE</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/HnZswssC8QL2</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>https://goo.gl/maps/8i7XHemjTpL2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>620 S WISCONSIN DR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GO IN THROUGH EMERGENCY ENTRANCE</t>
+          <t>5:30:00 AM COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Driver,
-Sante Fe,
-Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>C-STORE ONLY</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2731,17 +2916,21 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/m32L8HYJsFkLkhxb9</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -2749,36 +2938,38 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>After Aurora</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>CONDON OIL #135, OMRO</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2791,12 +2982,12 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -2811,63 +3002,85 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
+          <t>Courtney</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>163 E MAIN ST</t>
+          <t>OPEN PANTRY #9570, RACINE</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>ASCENSION ST JOSEPH-MAYFAIR RX #1106, TOSA</t>
+          <t>ASCENSION COMMUNITY RX #1100-WISC, RACINE</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -2879,12 +3092,14 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/w6KtjB6H4g72</t>
+          <t>2731 DURAND AVE</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -2897,32 +3112,36 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>201 N MAYFAIR RD</t>
+          <t>1244 WISCONSIN AVE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -2932,10 +3151,16 @@
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/boUkpED44a62</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -2948,32 +3173,36 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/efsuGG591Ms</t>
+          <t>https://goo.gl/maps/tu42wujVwN92</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Jeri</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -2982,23 +3211,13 @@
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3006,20 +3225,28 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PARK IN PARKING STRUCTURE.  ENTER THRU MAIN ENTRANCE</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -3027,7 +3254,7 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -3043,22 +3270,23 @@
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Sante Fe, Bring DC5's, 
-help Michelle</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3066,20 +3294,28 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
@@ -3088,48 +3324,53 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Camry available, Equip</t>
+          <t>Driver,
+Corolla,
+Equip</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 12:45</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Jacqui</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Camry</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3137,20 +3378,28 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
@@ -3159,24 +3408,24 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Kirsten</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 12:45, 1st DC5 Scan, work w/ Marcia</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -3185,6 +3434,8 @@
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3192,20 +3443,28 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1085 MILWAUKEE</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -3213,18 +3472,17 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -3233,6 +3491,8 @@
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3240,19 +3500,15 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>945 N 12TH ST</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -3261,12 +3517,12 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -3278,12 +3534,14 @@
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Madison Office</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3291,7 +3549,11 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/ocvCohDG8tChEG7r9</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3301,36 +3563,38 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>9:00 AM START</t>
+          <t>5:30 AM LEAVE TIME FROM OFFICE</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, work w/ Kirsten</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3338,30 +3602,52 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>*Reminder need a different scanner setup for this site!</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>5:15 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3373,97 +3659,163 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, 
-OAK CREEK</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>8809 S HOWELL AVE</t>
+          <t>CONDON OIL #175, RANDOLPH</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>20)</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>5:15 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1070, RACINE</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/1fZ4T4q9WR1Hexjb7</t>
+          <t>154 E KIENOW DR</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>21)</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3475,23 +3827,23 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>8400 WASHINGTON AVENUE</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PARK ACROSS THE STREET AT PICK N SAVE AND RIDE TOGETHER STORE HAS SMALL PARKING LOT</t>
+          <t>https://goo.gl/maps/gLRK63LNv182</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -3499,6 +3851,8 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3510,19 +3864,23 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/WsqKM5J2Bo42</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1433, MT PLEASANT</t>
-        </is>
-      </c>
+      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -3530,6 +3888,8 @@
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3544,28 +3904,16 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>13250 WASHINGTON AVE, SUITE 1A0043</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -3573,6 +3921,8 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3583,28 +3933,32 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>CONDON OIL #190, WAUPUN</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/hWixpCQuYhJ3PMrB9</t>
-        </is>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -3612,6 +3966,8 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3622,18 +3978,27 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>612 E MAIN ST</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
@@ -3647,6 +4012,8 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -3661,39 +4028,25 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>https://goo.gl/maps/JDEB8kGCMzC2</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -3712,28 +4065,108 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>@ Store,
+Equip</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Courtney</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA66"/>
+  <dimension ref="A1:Y74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, May 12</t>
+          <t>Sun, May 19</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, May 13</t>
+          <t>Mon, May 20</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, May 14</t>
+          <t>Tue, May 21</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 15</t>
+          <t>Wed, May 22</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 16</t>
+          <t>Thu, May 23</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 17</t>
+          <t>Fri, May 24</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,11 +467,9 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, May 18</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
+          <t>Sat, May 25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -499,8 +497,6 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -528,8 +524,6 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -561,8 +555,6 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -594,8 +586,6 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -627,8 +617,6 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -660,26 +648,20 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MOTHER'S DAY</t>
+          <t xml:space="preserve">5:15 AM MEET AT S RACEINE COURT (HWYS 43 &amp; Y) </t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4:45 AM REQUIRED MEET AT CAPITOL DR PICK N SAVE</t>
+          <t>5:00 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -687,7 +669,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -695,7 +677,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -711,33 +693,26 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ADDRESS TO THE MEET:
-5700 W CAPITOL DR, MILW</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -769,32 +744,26 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENTER THRU MATERNITY (3RD LEVEL) VISITOR ENTRANCE.  RX IS IN THE LOBBY</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -818,7 +787,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>METRO #371 +RX, MILWAUKEE</t>
+          <t>AURORA OUTPATIENT RX #1110, MILWAUKEE</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -826,32 +795,26 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>PICK #374, PEWAUKEE - CAPITOL DR</t>
+          <t>ALBRECHT'S DELAFIELD MARKET</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #200, MEQUON</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #221, PALMYRA</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>TIETZ'S PIGGLY WIGGLY #336, PLYMOUTH</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -859,7 +822,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #524 +RX, NORTHFIELD</t>
+          <t>MARIANO'S #531 +RX, SKOKIE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -867,7 +830,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #537 +RX, NAPERVILLE</t>
+          <t>MARIANO'S #506 +FC +RX, HOFFMAN ESTATES</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -875,7 +838,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1123 N VAN BUREN STREET</t>
+          <t>1575 N RIVERCENTER DRIVE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -883,28 +846,26 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1405 CAPITOL DRIVE</t>
+          <t>3255 GOLF RD</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6111 W MEQUON RD</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>117 W TAFT</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>1411 EASTERN AVE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -912,7 +873,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1822 WILLOW RD</t>
+          <t>3358 W TOUHY AVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -920,7 +881,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1300 S NAPER BLVD</t>
+          <t>2575 GOLF ROAD</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -928,7 +889,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/P9qm8u7dxgH2</t>
+          <t>https://goo.gl/maps/rULfaGpqQPG2</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -936,28 +897,26 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fM2WtjtDye32</t>
+          <t>https://goo.gl/maps/UZh6uE9Zs2H2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/vQEGbDwowNJ7UTyo7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/VvUw29M3hE72</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASCENSION ST JOSEPH RX-CHAMBERS #1103, MILW</t>
+          <t>https://goo.gl/maps/H1oQiRvmvRp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -965,7 +924,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jdSWvCFJ2cU2</t>
+          <t>https://goo.gl/maps/Dybn9qjgpUN2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -973,7 +932,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/zEFY7puewEn</t>
+          <t>https://goo.gl/maps/xDy3YHxAU3P2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -983,16 +942,10 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SET UP ON REG #5</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1000,27 +953,19 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>5000 W CHAMBERS  ROOM 1801</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>SET UP ON REG #1</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
@@ -1039,50 +984,78 @@
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>LIQUOR RESET-REMAPPED</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Red Van available, Equip</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
+      <c r="Y14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry, Equip</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>DJ</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/gRgCFNfwBUy</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1091,36 +1064,50 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Until noon</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
           <t>Carlie</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
+      <c r="Y15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1143,70 +1130,52 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
+          <t>Driver,
+Optima</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1218,78 +1187,59 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima,
-Rx</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ASCENSION ST FRANCIS RX #1107, MILWAUKEE</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1301,85 +1251,69 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Rx</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>2 AT ST LUKES, 6 AT ST MARY'S (NEED MINI POST IT NOTES)</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3237 S 16TH ST    ROOM 121</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
@@ -1388,75 +1322,69 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>ENTER THRU SURGICAL CENTER</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ckXW882eGXp</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
@@ -1465,231 +1393,222 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>6:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #201, CEDARBURG</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>W61 N286 WASHINGTON AVE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Driver,
 Red Van,
 Supv Rx</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC5-ITEM LEVEL   </t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/QamMdWSr16N2</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ASCENSION RX #1105, FRANKLIN-27TH ST</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
@@ -1698,72 +1617,77 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>ASCENSION ALL SAINTS HOSP WI AVE CAMPUS (ST LUKE'S), RACINE</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FEW GROC AISLES RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10101 S 27TH ST    ROOM 1005</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
@@ -1772,54 +1696,52 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>1320 WISCONSIN AVE</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1827,11 +1749,7 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/fQ4V9q61NUS2</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
@@ -1841,66 +1759,72 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>https://goo.gl/maps/raiuDa4wRko</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
@@ -1910,7 +1834,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1921,57 +1845,63 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC5-ITEM LEVEL </t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>5:30 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1983,7 +1913,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1994,65 +1924,64 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ASCENSION ALL SAINTS HOSP SPRING ST CAMPUS (ST MARY'S), RACINE</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Until 10:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ASCENSION AMG RAWSON AVE RX #1116, FRANKLIN</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -2064,7 +1993,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2075,12 +2004,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2089,67 +2018,77 @@
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>3801 SPRING ST</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Jerry S</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>@ Store, Until 1:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7400 W RAWSON AVE, SUITE 140</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2159,54 +2098,68 @@
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/PjumoiJbqD62</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:00</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>@ Store, Until 10:30</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/JDSt1uteEWoVQ3wg8</t>
+          <t>AURORA OUTPATIENT RX #1169 GREEN BAY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2219,196 +2172,251 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2845 GREENBRIER RD</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van, Equip</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:00</t>
-        </is>
-      </c>
+          <t>9:00 AM START</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>@ Store, Until 10:30</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/rneu9EfJWkGa7fvJ7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:00</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>@ Store, Until 10:30</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>PICK #846 +RX, WEST ALLIS - 108TH ST</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>SMOKE WORLD VAPE, BROOKFIELD</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2417,47 +2425,62 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van, Equip</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PICK #378, RACINE - CALEDONIA</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2625 S 108TH ST</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>17115 W BLUEMOUND RD</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2466,101 +2489,88 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>5111 DOUGLAS AVENUE</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1264, PORT WASHINGTON</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/BUUQissbQNk</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/o6BySGmshE5c9am29</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/b5CYjdz3kAC2</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1475 GRAND AVE</t>
+          <t>THEY NOW HAVE SIGNS UP NO STREET PARKING</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>6:15 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2574,7 +2584,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SMALL RESET-REMAPPED</t>
+          <t>5:30 AM START</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2582,38 +2592,44 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/eMESBveZrkcjkpYJ8</t>
+          <t>12:00 PM START</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2621,40 +2637,58 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1143 MENOM FALLS</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>@ Store, (comp)</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2664,67 +2698,44 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>@ Store,
-Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #6 HUBERTUS</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+          <t>N93 W14575 WHITTAKER WAY</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #493, RACINE</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2739,54 +2750,31 @@
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>1306 HWY 175</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/AJgcVD6yx75Kq3yS6</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>3441 SPRING ST</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2796,19 +2784,15 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1230, HOWARDS GROVE</t>
+          <t>ASCENSION COMMUNITY RX #1102-ATRIUM, RACINE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2817,33 +2801,19 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>9:00 AM START</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/8i7XHemjTpL2</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2853,62 +2823,52 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>620 S WISCONSIN DR</t>
+          <t>3811 SPRING ST</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>5:30:00 AM COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2918,58 +2878,48 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/m32L8HYJsFkLkhxb9</t>
+          <t>https://goo.gl/maps/HCpmGJRX9sG2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>SMOKE WORLD VAPE, WAUKESHA</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2977,129 +2927,85 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>ROTE OIL #7 MILWAUKEE</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Courtney</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>530 W SUNSET DRIVE</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #9570, RACINE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>5931 N 91ST ST</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>ASCENSION COMMUNITY RX #1100-WISC, RACINE</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/aogDHj45t6GWbbYP8</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2731 DURAND AVE</t>
+          <t>ROTE OIL #14 TREVOR (CITGO)</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -3107,60 +3013,42 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ASCENSION COMMUNITY RX #1101-SPRING ST, RACINE</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1244 WISCONSIN AVE</t>
+          <t xml:space="preserve">5:30 AM START </t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/boUkpED44a62</t>
+          <t>12617 ANTIOCH RD</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -3168,56 +3056,54 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3807 SPRING ST</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/tu42wujVwN92</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Jerry S</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3227,66 +3113,48 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PARK IN PARKING STRUCTURE.  ENTER THRU MAIN ENTRANCE</t>
+          <t>https://goo.gl/maps/345cLtjsHsD2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3294,307 +3162,243 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Josie</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ROTE OIL #8 ELM GROVE</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Driver,
-Corolla,
-Equip</t>
-        </is>
-      </c>
+          <t>1060 N ROCHESTER ST</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>13395 WATERTOWN PLANK RD</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45, 1st DC5 Scan, work w/ Marcia</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>ROTE OIL #13 TREVOR (BP)</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1085 MILWAUKEE</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>12511 ANTIOCH RD</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>945 N 12TH ST</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Madison Office</t>
+          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ocvCohDG8tChEG7r9</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>5:30 AM LEAVE TIME FROM OFFICE</t>
+          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>@ Store, work w/ Kirsten</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3602,17 +3406,13 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>*Reminder need a different scanner setup for this site!</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>5:15 AM MEET AT THE OFFICE</t>
+          <t>ROTE OIL #09 GREENFIELD</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3620,34 +3420,37 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>909 GREENWALD CT</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>@ Store,
+Camry, Equip</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3661,7 +3464,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>12345 W LAYTON AVE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3669,34 +3472,36 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
+          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3705,24 +3510,20 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3730,35 +3531,24 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>CONDON OIL #175, RANDOLPH</t>
+          <t xml:space="preserve">TO FOLLOW   </t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>20)</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>25406 75TH ST</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3767,55 +3557,41 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1070, RACINE</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>154 E KIENOW DR</t>
+          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>21)</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3823,27 +3599,43 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>8400 WASHINGTON AVENUE</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/gLRK63LNv182</t>
+          <t>122 ARROWHEAD DR</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -3851,8 +3643,6 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3860,13 +3650,21 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ROTE OIL #03 TWIN LAKES</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/WsqKM5J2Bo42</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -3874,13 +3672,17 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -3888,8 +3690,6 @@
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3897,23 +3697,35 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>475 N LAKE AVE</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -3921,8 +3733,6 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3930,35 +3740,27 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>CONDON OIL #190, WAUPUN</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>25555 75TH ST</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -3966,8 +3768,6 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3975,36 +3775,39 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>612 E MAIN ST</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -4012,8 +3815,6 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -4021,17 +3822,25 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/JDEB8kGCMzC2</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -4045,8 +3854,6 @@
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -4054,7 +3861,11 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ROTE OIL #04 GENOA CITY</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -4065,17 +3876,27 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -4083,45 +3904,42 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100 ELIZABETH LANE    </t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>@ Store,
-Equip</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -4129,32 +3947,24 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Courtney</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Madison Office</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4165,8 +3975,274 @@
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Until 2:00</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ROTE OIL #05  LAKE GENEVA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>300 PELLER RD</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, May 19</t>
+          <t>Sun, May 26</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, May 20</t>
+          <t>Mon, May 27</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, May 21</t>
+          <t>Tue, May 28</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 22</t>
+          <t>Wed, May 29</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 23</t>
+          <t>Thu, May 30</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 24</t>
+          <t>Fri, May 31</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, May 25</t>
+          <t>Sat, Jun 1</t>
         </is>
       </c>
     </row>
@@ -530,29 +530,57 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ICALS</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Bag 8</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>ICALS</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bags 1-4</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
     </row>
@@ -561,17 +589,21 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ICALS</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -582,14 +614,26 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bag 5, SB 11</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tuesday is a slow day due to Memorial day on Monday</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
@@ -613,8 +657,16 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lashaun </t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bag 6</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
     </row>
@@ -651,17 +703,17 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5:15 AM MEET AT S RACEINE COURT (HWYS 43 &amp; Y) </t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET BAYSHORE</t>
+          <t>*MEMORIAL DAY</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -669,7 +721,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:15 AM MEET OFFICE MEET</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -677,7 +729,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -685,7 +737,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t xml:space="preserve">4:15 AM MEET COLLEGE (SOUTHWEST) </t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -693,7 +745,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -702,19 +754,11 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -736,7 +780,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -744,7 +788,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -753,25 +797,17 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -787,7 +823,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1110, MILWAUKEE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -795,7 +831,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>ALBRECHT'S DELAFIELD MARKET</t>
+          <t>PICK #845 +RX, MILWAUKEE-LOOMIS</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -804,25 +840,17 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #221, PALMYRA</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>TIETZ'S PIGGLY WIGGLY #336, PLYMOUTH</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #531 +RX, SKOKIE</t>
+          <t>KOHN'S FILLING STATION, KEWASKUM</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -830,7 +858,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #506 +FC +RX, HOFFMAN ESTATES</t>
+          <t>MARIANO'S #526 +RX, SHOREWOOD</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -838,7 +866,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1575 N RIVERCENTER DRIVE</t>
+          <t>MARIANO'S #539 +RX, BRONZEVILLE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -846,7 +874,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3255 GOLF RD</t>
+          <t>3701 S 27TH ST</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -855,25 +883,17 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>117 W TAFT</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1411 EASTERN AVE</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3358 W TOUHY AVE</t>
+          <t>890 FOND DU LAC AVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -881,7 +901,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2575 GOLF ROAD</t>
+          <t>950 BROOK FOREST AVE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -889,7 +909,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/rULfaGpqQPG2</t>
+          <t>3857 S MARTIN LUTHER KING</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -897,7 +917,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/UZh6uE9Zs2H2</t>
+          <t>https://goo.gl/maps/BLy8vMxXBsA2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -906,25 +926,17 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/VvUw29M3hE72</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/H1oQiRvmvRp</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Dybn9qjgpUN2</t>
+          <t>https://goo.gl/maps/CJnRNDyortw</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -932,13 +944,17 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xDy3YHxAU3P2</t>
+          <t>https://goo.gl/maps/ieT41cP6AP42</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/xtUgo2RcwVm</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -959,30 +975,26 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SET UP ON REG #1</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>LIQUOR RESET-</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
@@ -996,82 +1008,36 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Red Van available, Equip</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry, Equip</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima, Equip</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Until noon</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
@@ -1080,74 +1046,65 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Driver,
-Optima</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
@@ -1156,7 +1113,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -1168,38 +1125,21 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>259 N FOND DU LAC AVE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1209,9 +1149,21 @@
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
@@ -1220,7 +1172,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -1232,33 +1184,21 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1268,10 +1208,14 @@
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2 AT ST LUKES, 6 AT ST MARY'S (NEED MINI POST IT NOTES)</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -1283,66 +1227,50 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ENTER THRU SURGICAL CENTER</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -1354,7 +1282,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1363,60 +1291,61 @@
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
@@ -1425,66 +1354,63 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #201, CEDARBURG</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -1496,7 +1422,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -1505,71 +1431,50 @@
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>W61 N286 WASHINGTON AVE</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>Driver,
-Sante Fe</t>
+Red Van</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-ITEM LEVEL   </t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
@@ -1587,61 +1492,41 @@
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/QamMdWSr16N2</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Supv Rx</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ASCENSION ALL SAINTS HOSP WI AVE CAMPUS (ST LUKE'S), RACINE</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
@@ -1653,7 +1538,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -1666,61 +1551,41 @@
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>FEW GROC AISLES RESET-REMAPPED</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1320 WISCONSIN AVE</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
@@ -1732,7 +1597,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -1752,38 +1617,34 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/raiuDa4wRko</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -1807,50 +1668,30 @@
       <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1224, SHEBOYGAN</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -1859,13 +1700,22 @@
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-ITEM LEVEL </t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
@@ -1874,7 +1724,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -1886,66 +1736,53 @@
       <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>5:30 AM MEET BAYSHORE</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>3400 UNION AVE, SUITE 1C-1006</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ASCENSION ALL SAINTS HOSP SPRING ST CAMPUS (ST MARY'S), RACINE</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
@@ -1954,7 +1791,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -1966,50 +1803,30 @@
       <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/oh7TcXwsTBYkDsmw5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2018,13 +1835,21 @@
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>3801 SPRING ST</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
@@ -2033,7 +1858,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2045,50 +1870,26 @@
       <c r="Y28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2097,69 +1898,73 @@
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/PjumoiJbqD62</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>@ Store, Until 10:30</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1169 GREEN BAY</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2168,49 +1973,57 @@
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2845 GREENBRIER RD</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2221,12 +2034,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2237,157 +2050,99 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>9:00 AM START</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>@ Store, Until 10:30</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/rneu9EfJWkGa7fvJ7</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>18)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>@ Store,
-Supv Rx</t>
+Rx</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>@ Store, Until 10:30</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19)</t>
+          <t>18)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2398,20 +2153,24 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t xml:space="preserve">18) </t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, BROOKFIELD</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -2423,59 +2182,54 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van, Equip</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
         <is>
           <t>19)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t xml:space="preserve">19) </t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>17115 W BLUEMOUND RD</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -2487,20 +2241,16 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2509,20 +2259,24 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>20)</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/o6BySGmshE5c9am29</t>
+          <t>AURORA OUTPATIENT RX #1262, MILWAUKEE</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -2539,35 +2293,27 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>THEY NOW HAVE SIGNS UP NO STREET PARKING</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>3003 W GOOD HOPE RD, SUITE 1129</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -2584,7 +2330,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5:30 AM START</t>
+          <t>N6485 COUNTY RD F</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2592,42 +2338,22 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>12:00 PM START</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/55ZX8sbcB762</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
     </row>
@@ -2637,17 +2363,13 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2655,37 +2377,21 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1143 MENOM FALLS</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>@ Store, (comp)</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
@@ -2696,44 +2402,44 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>ROTE OIL #6 HUBERTUS</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>N93 W14575 WHITTAKER WAY</t>
+          <t>ASCENSION SETON RX #1112, MILWAUKEE</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>COCA-COLA, MILWAUKEE</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
     </row>
@@ -2743,35 +2449,51 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1306 HWY 175</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/AJgcVD6yx75Kq3yS6</t>
+          <t>2301 N LAKE DR</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>11800 W BROWN DEER RD</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -2782,35 +2504,39 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>ASCENSION COMMUNITY RX #1102-ATRIUM, RACINE</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/fovW5S1B5ZD2</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>9:00 AM START</t>
+          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -2821,51 +2547,27 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3811 SPRING ST</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -2876,47 +2578,43 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/HCpmGJRX9sG2</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, WAUKESHA</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
@@ -2927,37 +2625,33 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ROTE OIL #7 MILWAUKEE</t>
+          <t>COCA-COLA, MILWAUKEE</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>ASCENSION CSM OZAUKEE RETAIL RX #1109, MEQUON</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>530 W SUNSET DRIVE</t>
-        </is>
-      </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
@@ -2970,37 +2664,33 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5931 N 91ST ST</t>
+          <t>11800 W BROWN DEER RD</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>13133 N PORT WASHINGTON RD,  SUITE G1</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/aogDHj45t6GWbbYP8</t>
-        </is>
-      </c>
+      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>ROTE OIL #14 TREVOR (CITGO)</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -3013,17 +2703,13 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>ASCENSION COMMUNITY RX #1101-SPRING ST, RACINE</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
+          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3031,19 +2717,23 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5:30 AM START </t>
+          <t>https://goo.gl/maps/ZV1UXpiCr4u</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>9:00 AM START</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>12617 ANTIOCH RD</t>
+          <t>VILLARD SHOP RITE, MILWAUKEE</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -3056,49 +2746,29 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>3807 SPRING ST</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
+          <t>5123 W VILLARD AVE</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
@@ -3111,37 +2781,45 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/345cLtjsHsD2</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>SMOKE WORLD VAPE, MILW-BRADY</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -3149,7 +2827,7 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>https://maps.app.goo.gl/e7gLkJnEfEdEK8D98</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -3165,40 +2843,44 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ROTE OIL #8 ELM GROVE</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1060 N ROCHESTER ST</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>1422 E BRADY ST</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
@@ -3208,50 +2890,53 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>13395 WATERTOWN PLANK RD</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/stP5CiWnmcaw4sMA7</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>ROTE OIL #13 TREVOR (BP)</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Red Van available, Equip</t>
+        </is>
+      </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
     </row>
@@ -3260,42 +2945,34 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>12511 ANTIOCH RD</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
@@ -3307,46 +2984,38 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>8:15 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
@@ -3358,22 +3027,14 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>9:00 AM START</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3381,7 +3042,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -3389,7 +3050,7 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>SMOKE WORLD VAPE, PUFF N UP, MILW-CAPITOL</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
@@ -3412,7 +3073,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>ROTE OIL #09 GREENFIELD</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3420,7 +3081,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>909 GREENWALD CT</t>
+          <t>COCA-COLA, MILWAUKEE</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -3428,27 +3089,14 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6900 W CAPITOL DR</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>@ Store,
-Camry, Equip</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3464,7 +3112,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>12345 W LAYTON AVE</t>
+          <t>SMOKE WORLD VAPE, WATERTOWN</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3472,7 +3120,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
+          <t>11800 W BROWN DEER RD</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -3480,26 +3128,14 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
+          <t>https://goo.gl/maps/vDKLCtsWm3wvSBNj7</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3508,22 +3144,14 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
+          <t>1907 MARKET WAY</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3531,17 +3159,13 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>25406 75TH ST</t>
-        </is>
-      </c>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -3555,37 +3179,37 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/wQQEXdVvpg4wrmb56</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
@@ -3599,41 +3223,37 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Ian</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>122 ARROWHEAD DR</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
@@ -3650,37 +3270,45 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>ROTE OIL #03 TWIN LAKES</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -3697,35 +3325,31 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>475 N LAKE AVE</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Red Van</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -3740,27 +3364,31 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>25555 75TH ST</t>
-        </is>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -3775,39 +3403,35 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+          <t>6:30 AM MEET OFFICE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -3822,25 +3446,17 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
@@ -3861,11 +3477,7 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>ROTE OIL #04 GENOA CITY</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -3873,24 +3485,16 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
@@ -3904,36 +3508,28 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100 ELIZABETH LANE    </t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
@@ -3947,21 +3543,21 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Madison Office</t>
+          <t>141 MAIN ST</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -3982,11 +3578,7 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3996,14 +3588,10 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Until 2:00</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4021,11 +3609,7 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
@@ -4052,20 +3636,28 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>ROTE OIL #05  LAKE GENEVA</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4083,20 +3675,29 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>300 PELLER RD</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -4114,11 +3715,7 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -4171,28 +3768,20 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Madison Office</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
@@ -4210,28 +3799,20 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, May 26</t>
+          <t>Sun, Jun 2</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, May 27</t>
+          <t>Mon, Jun 3</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, May 28</t>
+          <t>Tue, Jun 4</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 29</t>
+          <t>Wed, Jun 5</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 30</t>
+          <t>Thu, Jun 6</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 31</t>
+          <t>Fri, Jun 7</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Jun 1</t>
+          <t>Sat, Jun 8</t>
         </is>
       </c>
     </row>
@@ -530,57 +530,29 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ICALS</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ICALS</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Bags 1-4</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
     </row>
@@ -594,16 +566,8 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ICALS</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -614,33 +578,17 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bag 5, SB 11</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tuesday is a slow day due to Memorial day on Monday</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -657,16 +605,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lashaun </t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Bag 6</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
     </row>
@@ -675,11 +615,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -703,7 +639,11 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -713,7 +653,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>*MEMORIAL DAY</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -721,7 +661,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5:15 AM MEET OFFICE MEET</t>
+          <t>4:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -729,7 +669,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -737,7 +677,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4:15 AM MEET COLLEGE (SOUTHWEST) </t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -745,7 +685,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -754,11 +694,19 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -780,7 +728,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -788,7 +736,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -797,17 +745,25 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FOX BROS PIGGLY WIGGLY #093, OCONOMOWOC</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -823,7 +779,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>PICK #381, MUSKEGO</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -831,7 +787,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>PICK #845 +RX, MILWAUKEE-LOOMIS</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -840,17 +796,25 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>*SALE INVENTORY - FOX BROS BUYING</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1300 BROWN ST</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION, KEWASKUM</t>
+          <t>MARIANO'S #509 +RX, FRANKFORT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -858,7 +822,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #526 +RX, SHOREWOOD</t>
+          <t>MARIANO'S #501 +RX +OFFSITE RX, ARLINGTON HEIGHTS</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -866,7 +830,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #539 +RX, BRONZEVILLE</t>
+          <t>S74 W17005 JANESVILLE ROAD</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -874,7 +838,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3701 S 27TH ST</t>
+          <t>PICK #472 +RX, FOND DU LAC-PIONEER</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -883,17 +847,25 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #082, MAYVILLE</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/2K5yALCcUdM2</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>890 FOND DU LAC AVE</t>
+          <t>21001 S LAGRANGE RD</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -901,7 +873,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>950 BROOK FOREST AVE</t>
+          <t>802 E NORTHWEST HWY</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -909,7 +881,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>3857 S MARTIN LUTHER KING</t>
+          <t>https://goo.gl/maps/H8srKt8FVUp</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -917,7 +889,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/BLy8vMxXBsA2</t>
+          <t>55 W PIONEER RD</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -926,7 +898,11 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1440 HORICON ST</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -936,7 +912,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/CJnRNDyortw</t>
+          <t>https://goo.gl/maps/GfpVE3eArJM2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -944,7 +920,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ieT41cP6AP42</t>
+          <t>https://goo.gl/maps/ZNjAYKcq8772</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -952,65 +928,78 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xtUgo2RcwVm</t>
+          <t>5:15 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/Cccqh1Wg8xs</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/3nJCWDd6bxMw9Df6A</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>SET UP ON REG #6 OR 7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>**OFFSITE RX, ARLINGTON HEIGHTS</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>LIQUOR RESET-</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>SET UP ON REG #1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1019,198 +1008,295 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>@ Store,
+Trainer, work w/ Eva G</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1250 VILLAGE DR</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>5:00 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>*</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>https://maps.app.goo.gl/vthwUcrXyYaj6dDj9</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>LINK FOR RX ONLY</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>(Driver)</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>259 N FOND DU LAC AVE</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>@ Store,
+White Camry,
+Until 12:00</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Eva G</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>@ Store,
+1st Day, work w/ Carlie</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>4:15 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1222,67 +1308,94 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Supv Rx</t>
+          <t>@ Store,
+(Grafton),
+Trainer</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1290,238 +1403,345 @@
       <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Driver,
-Altima</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Rx</t>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 1:00</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>@ Store,
+After Aurora
+if needed</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>Until 12:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>@ Store, Until 11:45</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Louisa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>@ Store,
+Work w/ Marcia</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -1533,54 +1753,88 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kay</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>@ Store,
+Trainer</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -1592,117 +1846,172 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>@ Store, Until 11:45</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 1:00</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Until 11:00</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+(Grafton)</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1224, SHEBOYGAN</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Sante Fe</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -1710,160 +2019,183 @@
           <t>Sue</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 1:30</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3400 UNION AVE, SUITE 1C-1006</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>w/ Carlie</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Eva G</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, 1st DC5 Scan, work w/ Carlie</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/oh7TcXwsTBYkDsmw5</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -1875,58 +2207,59 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -1938,70 +2271,63 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MALICKI'S PIGGLY WIGGLY #342, OAK CREEK</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store,
+Supv Rx</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Kirsten</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 1:30</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -2013,17 +2339,21 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2201 E RAWSON AVE</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2034,39 +2364,39 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
     </row>
@@ -2076,7 +2406,11 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/r6Lve1UzasE2</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2085,40 +2419,40 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>FOX BROS PIGGLY WIGGLY #083, BEAVER DAM</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>@ Store,
-Rx</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+Trainer</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
     </row>
@@ -2137,12 +2471,12 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2151,29 +2485,29 @@
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18) </t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>810 PARK AVE</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr"/>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:30</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
     </row>
@@ -2182,56 +2516,57 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t xml:space="preserve">6:00 AM START   </t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Supv Rx</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19) </t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/y8AoS99KUVU2</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -2241,44 +2576,48 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>20)</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1262, MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -2288,30 +2627,62 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
+          <t>FOX BROS PIGGLY WIGGLY #091, SLINGER</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>3003 W GOOD HOPE RD, SUITE 1129</t>
+          <t>4:45 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
@@ -2323,34 +2694,63 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N6485 COUNTY RD F</t>
+          <t>1100 E COMMERCE BLVD</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/55ZX8sbcB762</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -2362,36 +2762,52 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
+          <t>https://goo.gl/maps/WgMCr1tJCE12</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
@@ -2401,45 +2817,53 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5:30 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>ASCENSION SETON RX #1112, MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>COCA-COLA, MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1032 FOND DU LAC</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
     </row>
@@ -2452,46 +2876,38 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2301 N LAKE DR</t>
+          <t>4:45 AM LEAVE TIME FROM THE OFFICE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>11800 W BROWN DEER RD</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>210 WISCONSIN AMERICAN DR,  SUITE 24</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
@@ -2507,34 +2923,50 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fovW5S1B5ZD2</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>https://maps.app.goo.gl/7eYhgLDismavDcYj6</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
@@ -2547,24 +2979,54 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5:00 AM MEET OFFICE</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>@ Store,
+Driver,
+Trainer</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -2578,44 +3040,69 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>6:00 AMSTART</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>@ Store,
+(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>LAKHBIR BP MOHAWK #7, MADISON</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>White Camry, Equip</t>
+        </is>
+      </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
     </row>
@@ -2625,35 +3112,55 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>COCA-COLA, MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>ASCENSION CSM OZAUKEE RETAIL RX #1109, MEQUON</t>
+          <t>4325 MOHAWK DR</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
@@ -2664,21 +3171,33 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1072 TWIN LAKES</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>11800 W BROWN DEER RD</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>13133 N PORT WASHINGTON RD,  SUITE G1</t>
+          <t>https://maps.app.goo.gl/PLqtoJ6NWQs5uGjt6</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
@@ -2688,11 +3207,7 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
@@ -2703,37 +3218,46 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>700 NORTH LAKE AVENUE SUITE 101</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>Eva G</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>@ Store,
+2nd Day, work w/ Carlie</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ZV1UXpiCr4u</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>9:00 AM START</t>
-        </is>
-      </c>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>VILLARD SHOP RITE, MILWAUKEE</t>
+          <t>5:30 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -2746,21 +3270,41 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/EJCh7QYTfkz4egwc8</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>5:15 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -2768,7 +3312,7 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>5123 W VILLARD AVE</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
@@ -2786,40 +3330,32 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>LAKHBIR CG MOBIL #5, MADISON</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, MILW-BRADY</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -2827,7 +3363,7 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/e7gLkJnEfEdEK8D98</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -2839,48 +3375,62 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van, Equip</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 1:00</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>605 COTTAGE GROVE RD</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1422 E BRADY ST</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>FOX BROS PIGGLY WIGGLY #086, PORT WASHINGTON</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
@@ -2890,53 +3440,58 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 1:00</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://maps.app.goo.gl/bmHVowFwiUmQqnQ86</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/stP5CiWnmcaw4sMA7</t>
+          <t>FOX BROS PIGGLY WIGGLY #084, WEST BEND</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Red Van available, Equip</t>
-        </is>
-      </c>
+          <t>101 W SEVEN HILLS RD</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
     </row>
@@ -2949,30 +3504,43 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Louisa</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>@ Store,
+Work w/ Marcia</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>2575 E WASHINGTON ST</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>https://maps.app.goo.gl/bDTjbGTBftHbSSuh9</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
@@ -2988,36 +3556,41 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8:15 AM MEET OFFICE</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>@ Store,
+Trainer</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>https://goo.gl/maps/v6j5Md5UXg82</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -3028,36 +3601,45 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>4:45 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>9:00 AM START</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>LAKHBIR CP MART AW #14, MADISON</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>SMOKE WORLD VAPE, PUFF N UP, MILW-CAPITOL</t>
-        </is>
-      </c>
+      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
     </row>
@@ -3067,36 +3649,58 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>COCA-COLA, MILWAUKEE</t>
+          <t>4601 COTTAGE GROVE RD</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>6900 W CAPITOL DR</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 12:00</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3106,13 +3710,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, WATERTOWN</t>
+          <t xml:space="preserve">5:30 AM MEET WATERTOWN PLANK </t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3120,21 +3728,33 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>11800 W BROWN DEER RD</t>
+          <t>https://maps.app.goo.gl/bjwT7M9WA23hoXd88</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/vDKLCtsWm3wvSBNj7</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
@@ -3145,32 +3765,54 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>LAKHBIR WG MOBIL #8, MADISON</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1907 MARKET WAY</t>
+          <t xml:space="preserve">6:00 AM START </t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe
+Until 9:00</t>
+        </is>
+      </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3180,40 +3822,69 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>699 S WHITNEY WAY</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/wQQEXdVvpg4wrmb56</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>White Camry, Equip</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>w/ Kim
+Until 9:00</t>
+        </is>
+      </c>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3223,44 +3894,68 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/dDkZaUKMLA3ANdv96</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>FOX BROS PIGGLY WIGGLY #090, JACKSON</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3270,52 +3965,68 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>W194 N16774 EAGLE DR</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
     </row>
@@ -3325,36 +4036,68 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Red Van</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/8bY4qRuqZNT2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
     </row>
@@ -3364,24 +4107,16 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP SYENE #16, FITCHBURG</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -3391,9 +4126,21 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
     </row>
@@ -3403,31 +4150,32 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2770 S SYENE RD</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Altima, Equip</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>6:30 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
@@ -3446,11 +4194,23 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/BGAVED5UHCh9zoeo8</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -3477,17 +4237,29 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
@@ -3497,7 +4269,11 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Madison Office</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
@@ -3508,21 +4284,33 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
+          <t>DAYBREAK, DELAFIELD</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
@@ -3532,7 +4320,11 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
@@ -3543,21 +4335,33 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP MART SOUTH #1, MADISON</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>141 MAIN ST</t>
+          <t>622 GENESEE ST</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -3578,17 +4382,33 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2570 RIMROCK RD</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
+          <t>https://goo.gl/maps/dNtyDnuiw6J2</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
@@ -3609,12 +4429,28 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/AeMqZ4iM1Pf323zs8</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -3639,9 +4475,21 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
@@ -3650,12 +4498,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>Red Van available, Equip</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -3674,9 +4522,21 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>White Camry, Equip</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -3689,15 +4549,10 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -3714,9 +4569,21 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -3741,12 +4608,28 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>4:45 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -3773,13 +4656,17 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Madison Office</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
@@ -3804,13 +4691,17 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
@@ -3825,6 +4716,595 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>LAKHBIR NP MOBIL #9, MADISON</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>SULLIVAN'S FOODS #242, MARENGO</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>3101 N SHERMAN AVE</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>202 LINDOW LANE</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/SNnQrwGgZvMobqnQ9</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/GrPtfaDKMT2RotRb9</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP MART NE #15, MADISON</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>4901 COMMERCIAL AVE</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/iYBAaHXs8ZRaWucF9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Driver,
+White Camry</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y90"/>
+  <dimension ref="A1:Y93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Jun 2</t>
+          <t>Sun, Jun 9</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Jun 3</t>
+          <t>Mon, Jun 10</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Jun 4</t>
+          <t>Tue, Jun 11</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Jun 5</t>
+          <t>Wed, Jun 12</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Jun 6</t>
+          <t>Thu, Jun 13</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Jun 7</t>
+          <t>Fri, Jun 14</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Jun 8</t>
+          <t>Sat, Jun 15</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,11 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -588,7 +592,11 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -615,7 +623,11 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -641,7 +653,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -661,7 +673,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -669,7 +681,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -677,7 +689,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -685,7 +697,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t xml:space="preserve">5:30 AM MEET AT S RACINE COURT </t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -696,7 +708,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -728,7 +740,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -747,7 +759,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>PIGGLY WIGGLY #220, MUSKEGO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -755,7 +767,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #093, OCONOMOWOC</t>
+          <t>PIGGLY WIGGLY #070, WEST ALLIS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -779,7 +791,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>PICK #381, MUSKEGO</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -798,7 +810,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>*SALE INVENTORY - FOX BROS BUYING</t>
+          <t>W189 S7847 RACINE AVE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -806,7 +818,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1300 BROWN ST</t>
+          <t>10282 W NATIONAL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -814,7 +826,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #509 +RX, FRANKFORT</t>
+          <t>MARIANO'S #513 +RX, WHEATON</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -822,7 +834,8 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #501 +RX +OFFSITE RX, ARLINGTON HEIGHTS</t>
+          <t>MARIANO'S #502 +RX, 
+VERNON HILLS</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -830,7 +843,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>S74 W17005 JANESVILLE ROAD</t>
+          <t>MARIANO'S #518 +RX, GLENVIEW</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -838,7 +851,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>PICK #472 +RX, FOND DU LAC-PIONEER</t>
+          <t>AURORA OUTPATIENT RX #1145 ELKHORN</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -849,7 +862,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #082, MAYVILLE</t>
+          <t>https://goo.gl/maps/3aRXzfmExPr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -857,7 +870,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/2K5yALCcUdM2</t>
+          <t>https://goo.gl/maps/zGMZZJVxurK2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -865,7 +878,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21001 S LAGRANGE RD</t>
+          <t>625 S MAIN ST</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -873,7 +886,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>802 E NORTHWEST HWY</t>
+          <t>1720 N MILWAUKEE AVENUE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -881,7 +894,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/H8srKt8FVUp</t>
+          <t>25 WAUKEGAN RD</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -889,7 +902,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>55 W PIONEER RD</t>
+          <t>W3985 COUNTY ROAD NN</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -898,21 +911,21 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1440 HORICON ST</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/GfpVE3eArJM2</t>
+          <t>https://maps.app.goo.gl/vYhjkFWiTisqXoRN9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -920,7 +933,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ZNjAYKcq8772</t>
+          <t>https://goo.gl/maps/ynVVx558fS22</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -928,7 +941,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5:15 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+          <t>https://goo.gl/maps/E7YkRP2q2272</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -936,7 +949,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Cccqh1Wg8xs</t>
+          <t>https://goo.gl/maps/DNeRzd2PfnuGBCUo6</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -944,84 +957,82 @@
       <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/3nJCWDd6bxMw9Df6A</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #6 OR 7</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>**OFFSITE RX, ARLINGTON HEIGHTS</t>
+          <t xml:space="preserve">SET UP ON LAST REG </t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>SET UP ON REG #1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer, work w/ Eva G</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1029,74 +1040,64 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1250 VILLAGE DR</t>
+          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>5:00 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe,
+Equip</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>(Driver)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1107,7 +1108,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1116,40 +1117,36 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/vthwUcrXyYaj6dDj9</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>LINK FOR RX ONLY</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>(Driver)</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
@@ -1157,31 +1154,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
@@ -1193,81 +1186,80 @@
           <t>Casey</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>@ Store,
-White Camry,
-Until 12:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eva G</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>@ Store,
-1st Day, work w/ Carlie</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
@@ -1282,21 +1274,30 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>Driver,
-Red Van</t>
+Gold Camry</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>4:15 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1306,59 +1307,40 @@
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>@ Store,
-(Grafton),
-Trainer</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
@@ -1367,18 +1349,26 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1386,16 +1376,18 @@
           <t>Ian</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>4:30 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1405,29 +1397,33 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Josie</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>(w/ Carlie)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1438,30 +1434,35 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>Driver,
+Altima</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1471,55 +1472,24 @@
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>@ Store,
-Until 1:00</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
@@ -1528,31 +1498,31 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Driver,
-Optima</t>
+Red Van</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1562,58 +1532,24 @@
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>@ Store,
-After Aurora
-if needed</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
@@ -1622,94 +1558,62 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Until 12:00</t>
+          <t>Driver,
+Gold Camry</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1157, STURGEON BAY</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Josie</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>@ Store, Until 11:45</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Louisa</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>@ Store,
-Work w/ Marcia</t>
-        </is>
-      </c>
+          <t>4:30 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
@@ -1718,47 +1622,43 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>1910 ALABAMA ST</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -1766,38 +1666,17 @@
       <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Kay</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>@ Store,
-Trainer</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
@@ -1806,52 +1685,45 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Rx
+(Train w/ Lashaun)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/PT62tX3aqSWcCC5G6</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -1859,38 +1731,17 @@
       <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>@ Store, Until 11:45</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>@ Store,
-Until 1:00</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
@@ -1899,7 +1750,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1910,70 +1761,45 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>@ Store,
-(Grafton)</t>
-        </is>
-      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #406, LANCASTER</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
@@ -1983,7 +1809,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1994,70 +1820,57 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>@ Store, Until 1:30</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>158 N WASHINGTON</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
@@ -2067,7 +1880,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2078,75 +1891,43 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>w/ Carlie</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Eva G</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>@ Store, 1st DC5 Scan, work w/ Carlie</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>https://goo.gl/maps/jFeseMTzfS32</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -2158,7 +1939,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2169,35 +1950,35 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
     </row>
@@ -2207,11 +1988,7 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
@@ -2221,47 +1998,54 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>5:00 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
@@ -2270,13 +2054,22 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MALICKI'S PIGGLY WIGGLY #342, OAK CREEK</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
@@ -2285,51 +2078,55 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>@ Store,
-Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>6:00 AM START</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:30</t>
-        </is>
-      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
     </row>
@@ -2338,10 +2135,14 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2201 E RAWSON AVE</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -2353,7 +2154,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2364,39 +2165,45 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx
+(Train w/ Lashaun)</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>DC5-FINANCIAL</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
     </row>
@@ -2405,13 +2212,22 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/r6Lve1UzasE2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2419,40 +2235,43 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #083, BEAVER DAM</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>@ Store,
-Trainer</t>
-        </is>
-      </c>
+          <t>PIGGLY WIGGLY #169, COTTAGE GROVE</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
     </row>
@@ -2461,8 +2280,16 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2471,12 +2298,12 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2486,28 +2313,16 @@
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>810 PARK AVE</t>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:30</t>
-        </is>
-      </c>
+          <t>421 W COTTAGE GROVE RD</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
     </row>
@@ -2518,55 +2333,50 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6:00 AM START   </t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>18)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>@ Store,
-Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/y8AoS99KUVU2</t>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/ysP4kdWtU542</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -2578,12 +2388,12 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -2591,19 +2401,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>19)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2613,7 +2423,11 @@
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
@@ -2629,12 +2443,12 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2642,50 +2456,38 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #091, SLINGER</t>
+          <t>PICK #357 +RX, GERMANTOWN</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>@ Store, Equip</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>4:45 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
     </row>
@@ -2696,12 +2498,12 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2709,51 +2511,38 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1100 E COMMERCE BLVD</t>
+          <t>N112 W16200 MEQUON RD</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>FOX BROS PIGGLY WIGGLY #087, HARTFORD</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
         <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr"/>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>@ Store, Until 12:00</t>
+        </is>
+      </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
     </row>
@@ -2764,12 +2553,12 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2777,38 +2566,43 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/WgMCr1tJCE12</t>
+          <t>https://goo.gl/maps/EHNPxYdtCp82</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1566 E SUMNER ST</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
         <is>
           <t>3)</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2819,12 +2613,12 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2832,35 +2626,35 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5:30 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+          <t>SET UP ON REG CLOSEST TOWARDS SERVICE COUNTER</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/aDpuMeDEHSz</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
         <is>
           <t>4)</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1032 FOND DU LAC</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
@@ -2877,37 +2671,33 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>4:45 AM LEAVE TIME FROM THE OFFICE</t>
+          <t>PIGGLY WIGGLY #170, WATERLOO</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
         <is>
           <t>5)</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>210 WISCONSIN AMERICAN DR,  SUITE 24</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
@@ -2923,53 +2713,49 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>810 N MONROE ST</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/7eYhgLDismavDcYj6</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
     </row>
@@ -2981,50 +2767,48 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t xml:space="preserve">6:00 AM START </t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>@ Store,
-Driver,
-Trainer</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/nBV5CGccWtE2</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -3042,67 +2826,50 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>6:00 AMSTART</t>
+          <t xml:space="preserve">DC5-FINANCIAL       </t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>@ Store,
-(w/ Carlie)</t>
+          <t>(Driver)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>LAKHBIR BP MOHAWK #7, MADISON</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>David</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>White Camry, Equip</t>
-        </is>
-      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
     </row>
@@ -3114,53 +2881,61 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>LAKHBIR WG MOBIL #8, MADISON</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>4325 MOHAWK DR</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Eva G</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4:30 AM MEET AT S RACINE COURT </t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
@@ -3173,41 +2948,61 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1072 TWIN LAKES</t>
+          <t>699 S WHITNEY WAY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
           <t>5)</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/PLqtoJ6NWQs5uGjt6</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>@ Store, after Condon</t>
+        </is>
+      </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
@@ -3220,44 +3015,63 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>700 NORTH LAKE AVENUE SUITE 101</t>
+          <t>https://maps.app.goo.gl/dDkZaUKMLA3ANdv96</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Eva G</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>@ Store,
-2nd Day, work w/ Carlie</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>5:30 AM MEET BAYSHORE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -3272,47 +3086,63 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/EJCh7QYTfkz4egwc8</t>
+          <t xml:space="preserve">TO FOLLOW </t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>7)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>5:15 AM MEET WATERTOWN PLANK</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>SULLIVAN'S FOODS #295 +ACE, WINNEBAGO</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
@@ -3325,45 +3155,61 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
           <t>8)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>LAKHBIR CG MOBIL #5, MADISON</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>@ Store, after Condon</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>703 N ELIDA STREET</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -3375,60 +3221,62 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van, Equip</t>
-        </is>
-      </c>
+          <t>LAKHBIR CP SYENE #16, FITCHBURG</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>9)</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>@ Store,
-Until 1:00</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>605 COTTAGE GROVE RD</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #086, PORT WASHINGTON</t>
+          <t>https://goo.gl/maps/XJm8iLALryeWSpAZ6</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
@@ -3440,57 +3288,40 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>2770 S SYENE RD</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Kirsten</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>@ Store,
-Until 1:00</t>
+          <t>Until 11:00</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/bmHVowFwiUmQqnQ86</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>FOX BROS PIGGLY WIGGLY #084, WEST BEND</t>
-        </is>
-      </c>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>101 W SEVEN HILLS RD</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -3501,49 +3332,53 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/BGAVED5UHCh9zoeo8</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Louisa</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>@ Store,
-Work w/ Marcia</t>
+          <t>(w/ Carlie)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>2575 E WASHINGTON ST</t>
-        </is>
-      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/bDTjbGTBftHbSSuh9</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>@ Store, Equip,
+(Groc Supv)</t>
+        </is>
+      </c>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -3553,30 +3388,33 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Marcia</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>4:45 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -3584,14 +3422,27 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/v6j5Md5UXg82</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
     </row>
@@ -3603,43 +3454,54 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4:45 AM OFFICE LEAVE TIME</t>
+          <t xml:space="preserve">DC5-FINANCIAL   </t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>LAKHBIR CP MART AW #14, MADISON</t>
+          <t xml:space="preserve">6:00 AM START </t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima, Equip</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
     </row>
@@ -3651,54 +3513,56 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>LAKHBIR CP MART SOUTH #1, MADISON</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>4601 COTTAGE GROVE RD</t>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>PIGGLY WIGGLY #168, EDGERTON</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>@ Store,
-Until 12:00</t>
+          <t>Ace Side</t>
         </is>
       </c>
       <c r="X54" t="inlineStr"/>
@@ -3712,47 +3576,39 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>2570 RIMROCK RD</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5:30 AM MEET WATERTOWN PLANK </t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/bjwT7M9WA23hoXd88</t>
+          <t>LAKHBIR BP MOHAWK #7, MADISON</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>1211 N MAIN ST</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
@@ -3767,50 +3623,44 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LAKHBIR WG MOBIL #8, MADISON</t>
+          <t>https://maps.app.goo.gl/AeMqZ4iM1Pf323zs8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6:00 AM START </t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>4325 MOHAWK DR</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/9YbLUf3aGUH2</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Driver,
-Sante Fe
-Until 9:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
@@ -3822,67 +3672,42 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>699 S WHITNEY WAY</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>White Camry, Equip</t>
-        </is>
-      </c>
+          <t>https://maps.app.goo.gl/PLqtoJ6NWQs5uGjt6</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>w/ Kim
-Until 9:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
@@ -3893,62 +3718,62 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/dDkZaUKMLA3ANdv96</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #090, JACKSON</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW </t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -3964,46 +3789,46 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>W194 N16774 EAGLE DR</t>
+          <t>FOX BROS PIGGLY WIGGLY #089, HUBERTUS</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Palmer</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC5-FINANCIAL  </t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4014,12 +3839,12 @@
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -4035,46 +3860,46 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/8bY4qRuqZNT2</t>
+          <t>1234 HWY 175</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>LAKHBIR CG MOBIL #5, MADISON</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Jeri</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -4085,17 +3910,18 @@
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Ace Side</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -4107,38 +3933,55 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>LAKHBIR CP SYENE #16, FITCHBURG</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/k8v61779c9p</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>605 COTTAGE GROVE RD</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Ace Side</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -4150,41 +3993,52 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2770 S SYENE RD</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima, Equip</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/bmHVowFwiUmQqnQ86</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
     </row>
@@ -4194,40 +4048,65 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/BGAVED5UHCh9zoeo8</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>@ Store,
+Ace Side</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -4237,44 +4116,64 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t xml:space="preserve">DC5-FINANCIAL   </t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Madison Office</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
     </row>
@@ -4284,48 +4183,65 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Jeri</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>DAYBREAK, DELAFIELD</t>
+          <t>LAKHBIR CP MART AW #14, MADISON</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>@ Store,
+Ace Supv</t>
+        </is>
+      </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
     </row>
@@ -4335,33 +4251,29 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>LAKHBIR CP MART SOUTH #1, MADISON</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Josie</t>
+          <t>Eva G</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>622 GENESEE ST</t>
+          <t>4601 COTTAGE GROVE RD</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -4370,9 +4282,22 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>@ Store,
+Ace Side</t>
+        </is>
+      </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
     </row>
@@ -4382,33 +4307,29 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2570 RIMROCK RD</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/dNtyDnuiw6J2</t>
+          <t>https://maps.app.goo.gl/bjwT7M9WA23hoXd88</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
@@ -4429,26 +4350,22 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/AeMqZ4iM1Pf323zs8</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4457,7 +4374,11 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:30 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -4477,17 +4398,17 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Savannah</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4498,21 +4419,30 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Red Van available, Equip</t>
+          <t>White Camry
+Equip</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>4:45 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -4522,25 +4452,25 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>White Camry, Equip</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
@@ -4549,17 +4479,29 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -4569,36 +4511,56 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Palmer</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP WEST #11, MADISON</t>
+        </is>
+      </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -4608,40 +4570,44 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4:45 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>@ Store, Until 10:30</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>6702 MINERAL POINT RD</t>
+        </is>
+      </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>LAKHBIR BP COMMERCIAL #10, MADISON</t>
+        </is>
+      </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -4656,27 +4622,27 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/u6JziHHvPAFDhbCTA</t>
+        </is>
+      </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>4102 COMMERICAL AVE</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
@@ -4691,27 +4657,27 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/nBvaVpu2arFW9mTu8</t>
+        </is>
+      </c>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
@@ -4728,25 +4694,29 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>LAKHBIR NP MOBIL #9, MADISON</t>
+          <t>4:45 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>SULLIVAN'S FOODS #242, MARENGO</t>
-        </is>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
@@ -4763,25 +4733,29 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>3101 N SHERMAN AVE</t>
+          <t xml:space="preserve">6:00 AM START </t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>202 LINDOW LANE</t>
-        </is>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>LAKHBIR GAMMON BP #12, MADISON</t>
+        </is>
+      </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
@@ -4798,25 +4772,29 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/SNnQrwGgZvMobqnQ9</t>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/GrPtfaDKMT2RotRb9</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>699 S GAMMON RD</t>
+        </is>
+      </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>LAKHBIR MS MOBIL #4, MADISON</t>
+        </is>
+      </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
@@ -4833,7 +4811,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>LAKHBIR NP MOBIL #9, MADISON</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4843,11 +4821,19 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/xn9rk4qzwpnZm3Jj9</t>
+        </is>
+      </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>3019 E WASHINGTON AVE</t>
+        </is>
+      </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
@@ -4864,33 +4850,29 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>3101 N SHERMAN AVE</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/Kpi5RsNj91eBCKx88</t>
+        </is>
+      </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
@@ -4907,33 +4889,29 @@
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>LAKHBIR CP MART NE #15, MADISON</t>
+          <t>https://maps.app.goo.gl/SNnQrwGgZvMobqnQ9</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
@@ -4950,33 +4928,29 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4901 COMMERCIAL AVE</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>LAKHBIR VR MOBIL #6, MADISON</t>
+        </is>
+      </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
@@ -4993,33 +4967,29 @@
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/iYBAaHXs8ZRaWucF9</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>4601 VERONA RD</t>
+        </is>
+      </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>LAKHBIR BP EAST #2, MADISON</t>
+        </is>
+      </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
@@ -5034,27 +5004,31 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP MART NE #15, MADISON</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/R5BjsCpnN3fE746N9</t>
+        </is>
+      </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2702 E WASHINGTON AVE</t>
+        </is>
+      </c>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
@@ -5068,44 +5042,28 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>4901 COMMERCIAL AVE</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/eD1oEYfBoN2jg6bP8</t>
+        </is>
+      </c>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
@@ -5119,30 +5077,33 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Driver,
-White Camry</t>
-        </is>
-      </c>
+          <t>https://maps.app.goo.gl/iYBAaHXs8ZRaWucF9</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
@@ -5159,33 +5120,45 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
     </row>
@@ -5198,20 +5171,53 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>White Camry
+Equip</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Sante Fe</t>
+        </is>
+      </c>
       <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
@@ -5225,9 +5231,21 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
@@ -5237,9 +5255,22 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Driver,
+White Camry</t>
+        </is>
+      </c>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
     </row>
@@ -5252,13 +5283,21 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -5268,9 +5307,21 @@
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>@ Store (After c-store if needed)</t>
+        </is>
+      </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
     </row>
@@ -5284,11 +5335,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
@@ -5305,6 +5352,95 @@
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y93"/>
+  <dimension ref="A1:Y87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Jun 9</t>
+          <t>Sun, Jun 16</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Jun 10</t>
+          <t>Mon, Jun 17</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Jun 11</t>
+          <t>Tue, Jun 18</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Jun 12</t>
+          <t>Wed, Jun 19</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Jun 13</t>
+          <t>Thu, Jun 20</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Jun 14</t>
+          <t>Fri, Jun 21</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Jun 15</t>
+          <t>Sat, Jun 22</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>FATHER'S DAY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -673,7 +673,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -681,7 +681,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -697,7 +697,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5:30 AM MEET AT S RACINE COURT </t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -706,17 +706,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -748,7 +744,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -757,17 +753,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #220, MUSKEGO</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #070, WEST ALLIS</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -799,7 +791,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>METRO #301 +RX, BROOKFIELD</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -808,17 +800,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>W189 S7847 RACINE AVE</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10282 W NATIONAL</t>
+          <t>PIGGLY WIGGLY #037, RACINE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -826,7 +814,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #513 +RX, WHEATON</t>
+          <t>MARIANO'S #538 +RX, BROADWAY</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -834,8 +822,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #502 +RX, 
-VERNON HILLS</t>
+          <t>MARIANO'S #525 +RX, PARK RIDGE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -843,7 +830,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #518 +RX, GLENVIEW</t>
+          <t>MARIANO'S #542 +RX, BANNOCKBURN</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -851,7 +838,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1145 ELKHORN</t>
+          <t>17630 W BLUEMOUND</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -860,17 +847,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/3aRXzfmExPr</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/zGMZZJVxurK2</t>
+          <t>5600 SPRING ST</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -878,7 +861,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>625 S MAIN ST</t>
+          <t>3030 N BROADWAY #100</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -886,7 +869,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1720 N MILWAUKEE AVENUE</t>
+          <t>1900 S CUMBERLAND DR</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -894,7 +877,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>25 WAUKEGAN RD</t>
+          <t>2999 WAUKEGAN RD</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -902,7 +885,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>W3985 COUNTY ROAD NN</t>
+          <t>https://goo.gl/maps/Uv69q4HmCNQ2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -917,7 +900,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+          <t>https://goo.gl/maps/vkH7vLz9Zrx</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -925,7 +908,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/vYhjkFWiTisqXoRN9</t>
+          <t>https://goo.gl/maps/bMv5fDgQsNT2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -933,7 +916,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ynVVx558fS22</t>
+          <t>https://goo.gl/maps/39qeNV6tuWU2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -941,7 +924,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/E7YkRP2q2272</t>
+          <t>https://goo.gl/maps/iQpQKzHwQVT2</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -949,7 +932,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/DNeRzd2PfnuGBCUo6</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -957,21 +940,9 @@
       <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -980,25 +951,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>SET UP ON SECOND FLOOR REG #4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SET UP ON LAST REG </t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -1008,16 +971,8 @@
       <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
@@ -1032,7 +987,8 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store,
+Equip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1040,17 +996,37 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
@@ -1059,30 +1035,20 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Driver,
-Sante Fe,
-Equip</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Mai</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
@@ -1092,12 +1058,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>(Driver)</t>
+          <t>Driver,
+Red Van</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1108,7 +1075,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1117,23 +1084,36 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2nd week</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>Driver,
+Red Van</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -1144,7 +1124,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -1152,16 +1132,8 @@
       <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
@@ -1183,71 +1155,63 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Driver,
-Sante Fe</t>
+Altima</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>Driver,
+Red Van</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
@@ -1256,10 +1220,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2nd DC5 Financial</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
@@ -1268,67 +1236,57 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Driver,
-Gold Camry</t>
+          <t>2nd week</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -1337,7 +1295,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1356,38 +1314,36 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>4:30 AM OFFICE LEAVE TIME</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1395,21 +1351,9 @@
       <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -1418,12 +1362,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>(w/ Carlie)</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1434,51 +1378,54 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Robyn</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Driver,
-Altima</t>
+          <t>2nd week</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2nd week</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
@@ -1487,8 +1434,16 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
@@ -1498,44 +1453,56 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -1558,44 +1525,55 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Driver,
-Gold Camry</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1157, STURGEON BAY</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -1610,7 +1588,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4:30 AM MEET AT THE OFFICE</t>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1622,46 +1600,64 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1910 ALABAMA ST</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
@@ -1673,7 +1669,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1685,48 +1681,63 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx
-(Train w/ Lashaun)</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/PT62tX3aqSWcCC5G6</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Until 9:00</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
     </row>
@@ -1738,7 +1749,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1750,7 +1761,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1761,31 +1772,51 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
@@ -1797,7 +1828,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #406, LANCASTER</t>
+          <t>DHILLON'S BP, MAYVILLE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1809,54 +1840,59 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
@@ -1868,7 +1904,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>158 N WASHINGTON</t>
+          <t>1400 HORICON ST</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1880,7 +1916,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1891,31 +1927,51 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2nd week</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
@@ -1927,7 +1983,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jFeseMTzfS32</t>
+          <t>https://goo.gl/maps/UAmrX3SR6jD2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1939,7 +1995,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1950,34 +2006,47 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>@ Store,
+Trainer</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>(w/ Carlie)</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -1988,7 +2057,11 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5:00 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
@@ -1998,39 +2071,41 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Trainer</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>(w/ Carlie)</t>
+          <t>@ Store,
+Supv Rx</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -2039,13 +2114,21 @@
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>5:00 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
@@ -2054,22 +2137,9 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
@@ -2078,7 +2148,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2089,12 +2159,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2103,29 +2173,12 @@
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -2137,70 +2190,37 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx
-(Train w/ Lashaun)</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -2214,18 +2234,18 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store
+(w/ Trevor)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2233,42 +2253,22 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #169, COTTAGE GROVE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -2282,44 +2282,49 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>@ Store
+(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:15 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>421 W COTTAGE GROVE RD</t>
+          <t>2 SISTERS PIGGLY WIGGLY #266, MARKESAN</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -2331,50 +2336,38 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #092, HARTLAND</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ysP4kdWtU542</t>
+          <t>450 N MARGARET ST</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -2386,52 +2379,41 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>METRO #892 +RX, MENOMONEE FALLS - 
+COUNTY LINE RD</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>505 SOUTH COTTONWOOD</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/nVgmJAwKdEjhqQAt6</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -2441,14 +2423,10 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2456,38 +2434,30 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>PICK #357 +RX, GERMANTOWN</t>
+          <t>N95 W18351 COUNTY LINE RD</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>OPEN PANTRY #493, RACINE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/3fKEhu9Q6Q52</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
     </row>
@@ -2496,14 +2466,10 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2511,36 +2477,40 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N112 W16200 MEQUON RD</t>
+          <t>https://goo.gl/maps/KutaqrX9XEx</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>3441 SPRING ST</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #087, HARTFORD</t>
+          <t>RESETS-REMAPPED</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>@ Store, Until 12:00</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -2551,14 +2521,10 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2566,7 +2532,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/EHNPxYdtCp82</t>
+          <t>SET UP LAST REG BY SELF C/O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2574,22 +2540,18 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>https://goo.gl/maps/8i7XHemjTpL2</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>1566 E SUMNER ST</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -2599,7 +2561,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Driver,
+          <t>@ Store,
 Optima</t>
         </is>
       </c>
@@ -2611,14 +2573,10 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>DHILLON'S STATION HUSTIS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2626,7 +2584,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SET UP ON REG CLOSEST TOWARDS SERVICE COUNTER</t>
+          <t>5:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2634,30 +2592,42 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t xml:space="preserve">TO FOLLOW </t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/aDpuMeDEHSz</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr"/>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
     </row>
@@ -2667,40 +2637,56 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>326 W JUNEAU ST</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>5:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #170, WATERLOO</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr"/>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
     </row>
@@ -2710,45 +2696,61 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/2MvPuCPioicrHiKc6</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>810 N MONROE ST</t>
+          <t>OPEN PANTRY #9570, RACINE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -2765,45 +2767,41 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6:00 AM START </t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>(w/ Trevor)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/nBV5CGccWtE2</t>
+          <t>2731 DURAND AVE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -2812,9 +2810,21 @@
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
     </row>
@@ -2823,42 +2833,50 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL       </t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>(Driver)</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/boUkpED44a62</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kirsten</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -2878,50 +2896,42 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LAKHBIR WG MOBIL #8, MADISON</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Eva G</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -2931,11 +2941,7 @@
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4:30 AM MEET AT S RACINE COURT </t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
@@ -2945,62 +2951,75 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>699 S WHITNEY WAY</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Driver,
+White Camry</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Jeri</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Jerry S</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>@ Store, after Condon</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Milwaukee Office</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -3013,68 +3032,53 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/dDkZaUKMLA3ANdv96</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+White Camry</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>After Metro</t>
+        </is>
+      </c>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
     </row>
@@ -3084,67 +3088,31 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW </t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>SULLIVAN'S FOODS #295 +ACE, WINNEBAGO</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -3157,61 +3125,41 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL </t>
+          <t>4:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2nd week</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Ron</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>@ Store, after Condon</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>703 N ELIDA STREET</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -3224,61 +3172,41 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LAKHBIR CP SYENE #16, FITCHBURG</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>4:30 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Ron</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/XJm8iLALryeWSpAZ6</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
@@ -3291,14 +3219,14 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2770 S SYENE RD</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3306,18 +3234,22 @@
           <t>Stephanie</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1067, HARTLAND</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -3334,51 +3266,46 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/BGAVED5UHCh9zoeo8</t>
+          <t>SULLIVAN'S FOODS #225, FREEPORT</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>(w/ Carlie)</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>600 WALNUT RIDGE DR</t>
+        </is>
+      </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>@ Store, Equip,
-(Groc Supv)</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -3390,31 +3317,31 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>2002 W GALENA AVE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>(w/ Carlie)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>4:45 AM OFFICE LEAVE TIME</t>
+          <t>DHILLON'S BP, MARKESAN</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -3422,27 +3349,14 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>https://goo.gl/maps/sZu3Qrsu6zC2</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
     </row>
@@ -3454,19 +3368,19 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL   </t>
+          <t>https://goo.gl/maps/YcFP9FTjTEs94iQh7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3478,29 +3392,17 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6:00 AM START </t>
+          <t>N1894 WI-44 (HWY 44 &amp; 73)</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
@@ -3513,19 +3415,19 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LAKHBIR CP MART SOUTH #1, MADISON</t>
+          <t>WE SET UP IN THE BACKROOM BY END OF FROZEN AISLES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3537,34 +3439,30 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL </t>
+          <t>https://goo.gl/maps/uRQ5w6AXAun5KEMW7</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #168, EDGERTON</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Ace Side</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3574,43 +3472,39 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2570 RIMROCK RD</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>LAKHBIR BP MOHAWK #7, MADISON</t>
+          <t>4:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>1211 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
@@ -3620,49 +3514,37 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/AeMqZ4iM1Pf323zs8</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>4325 MOHAWK DR</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/9YbLUf3aGUH2</t>
-        </is>
-      </c>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3671,45 +3553,54 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Driver,
+Tan Camry</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/PLqtoJ6NWQs5uGjt6</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3720,67 +3611,52 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW </t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>@ Store
+(w/ Trevor)</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3791,67 +3667,52 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Palmer</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #089, HUBERTUS</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL  </t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>@ Store
+(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DHILLON'S HARTLAND VILLAGE MART</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
     </row>
@@ -3862,12 +3723,12 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3879,51 +3740,26 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1234 HWY 175</t>
+          <t>OPEN PANTRY #605, BAYSIDE</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>LAKHBIR CG MOBIL #5, MADISON</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Jeri</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>301 E CAPITOL DR</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>@ Store,
-Ace Side</t>
-        </is>
-      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
     </row>
@@ -3932,58 +3768,45 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/k8v61779c9p</t>
+          <t>501 W BROWN DEER RD</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>605 COTTAGE GROVE RD</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/D7P2Btvsg3y</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>@ Store,
-Ace Side</t>
-        </is>
-      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
     </row>
@@ -3992,53 +3815,45 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/pQaSRAn88Vh6DAQ58</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/bmHVowFwiUmQqnQ86</t>
+          <t>5:15 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
     </row>
@@ -4047,66 +3862,57 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Tan Camry available, Equip</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Justin</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>@ Store,
-Ace Side</t>
-        </is>
-      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -4115,65 +3921,53 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL   </t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
     </row>
@@ -4186,62 +3980,42 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>OPEN PANTRY #612, BROOKFIELD</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>LAKHBIR CP MART AW #14, MADISON</t>
+          <t>DHILLON'S BP, NEOSHO</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+After Aurora</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>@ Store,
-Ace Supv</t>
-        </is>
-      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
     </row>
@@ -4254,26 +4028,18 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Eva G</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>17235 W BLUEMOUND RD</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>4601 COTTAGE GROVE RD</t>
+          <t>446 S SCHUYER ST</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -4282,22 +4048,9 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>@ Store,
-Ace Side</t>
-        </is>
-      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
     </row>
@@ -4310,26 +4063,18 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/awRYbmypZ4H2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/bjwT7M9WA23hoXd88</t>
+          <t>https://goo.gl/maps/cqKUT41W2wM2</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
@@ -4353,21 +4098,13 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -4376,7 +4113,7 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>4:30 AM OFFICE LEAVE TIME</t>
+          <t>4:45 AM MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="S68" t="inlineStr"/>
@@ -4396,21 +4133,13 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
@@ -4419,13 +4148,13 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>White Camry
-Equip</t>
+          <t>Driver,
+Sante Fe, Equip</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -4438,11 +4167,7 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>4:45 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -4456,21 +4181,13 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>OPEN PANTRY #614, MILWAUKEE</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
@@ -4479,29 +4196,21 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -4515,21 +4224,13 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>3100 S 76TH ST</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
@@ -4538,29 +4239,21 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>LAKHBIR CP WEST #11, MADISON</t>
+          <t>DHILLON'S STATION 51 LLC, JANESVILLE</t>
         </is>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -4574,21 +4267,13 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>@ Store, Until 10:30</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/fpg1rAd58h22</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -4597,17 +4282,13 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>6702 MINERAL POINT RD</t>
+          <t>1620 W US HWY 14</t>
         </is>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>LAKHBIR BP COMMERCIAL #10, MADISON</t>
-        </is>
-      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -4632,17 +4313,13 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/u6JziHHvPAFDhbCTA</t>
+          <t>https://goo.gl/maps/AMes3hiS3DN1CYZx6</t>
         </is>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>4102 COMMERICAL AVE</t>
-        </is>
-      </c>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
@@ -4656,28 +4333,40 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>White Camry available, Equip</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>5:15 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride - Go straight to the store</t>
         </is>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/nBvaVpu2arFW9mTu8</t>
-        </is>
-      </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
@@ -4691,32 +4380,32 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>4:45 AM OFFICE LEAVE TIME</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
@@ -4730,32 +4419,44 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">6:00 AM START </t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>LAKHBIR GAMMON BP #12, MADISON</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
@@ -4770,31 +4471,36 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC5-FINANCIAL </t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>DHILLON'S STATION HWY 33, HARTFORD</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>699 S GAMMON RD</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>@ Store
+(w/ Trevor)</t>
+        </is>
+      </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>LAKHBIR MS MOBIL #4, MADISON</t>
-        </is>
-      </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
@@ -4809,31 +4515,31 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>LAKHBIR NP MOBIL #9, MADISON</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>W346 LUEDTKE LANE</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xn9rk4qzwpnZm3Jj9</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>3019 E WASHINGTON AVE</t>
-        </is>
-      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
@@ -4848,31 +4554,31 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>3101 N SHERMAN AVE</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/sBbGZTSeFYGcwxAe7</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/Kpi5RsNj91eBCKx88</t>
-        </is>
-      </c>
+      <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
@@ -4887,31 +4593,32 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/SNnQrwGgZvMobqnQ9</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Driver,
+White Camry</t>
+        </is>
+      </c>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
@@ -4926,31 +4633,45 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Driver,
+Tan Camry, Equip</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>LAKHBIR VR MOBIL #6, MADISON</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr"/>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>@ Store
+(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
@@ -4965,31 +4686,27 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>4601 VERONA RD</t>
-        </is>
-      </c>
+      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>LAKHBIR BP EAST #2, MADISON</t>
-        </is>
-      </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
@@ -5004,31 +4721,27 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>LAKHBIR CP MART NE #15, MADISON</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/R5BjsCpnN3fE746N9</t>
-        </is>
-      </c>
+      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>2702 E WASHINGTON AVE</t>
-        </is>
-      </c>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
@@ -5043,11 +4756,7 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>4901 COMMERCIAL AVE</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
@@ -5059,11 +4768,7 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/eD1oEYfBoN2jg6bP8</t>
-        </is>
-      </c>
+      <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
@@ -5078,32 +4783,16 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/iYBAaHXs8ZRaWucF9</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
@@ -5125,40 +4814,20 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
     </row>
@@ -5171,275 +4840,31 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>White Camry
-Equip</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>After Dhillons</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Sante Fe</t>
-        </is>
-      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Palmer</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Driver,
-White Camry</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Ron</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>@ Store (After c-store if needed)</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week2.xlsx
+++ b/Week2.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y87"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Jun 16</t>
+          <t>Sun, Jul 7</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Jun 17</t>
+          <t>Mon, Jul 8</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Jun 18</t>
+          <t>Tue, Jul 9</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Jun 19</t>
+          <t>Wed, Jul 10</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Jun 20</t>
+          <t>Thu, Jul 11</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Jun 21</t>
+          <t>Fri, Jul 12</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Jun 22</t>
+          <t>Sat, Jul 13</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,11 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Optima appointment</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -651,11 +655,7 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FATHER'S DAY</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -673,7 +673,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -681,7 +681,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -689,7 +689,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -697,7 +697,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -744,7 +744,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -791,7 +791,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>METRO #301 +RX, BROOKFIELD</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -806,7 +806,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #037, RACINE</t>
+          <t>PIGGLY WIGGLY #207, LAKE GENEVA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -814,7 +814,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #538 +RX, BROADWAY</t>
+          <t>MARIANO'S #511 +RX, ELMHURST</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -822,7 +822,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #525 +RX, PARK RIDGE</t>
+          <t>MARIANO'S #514 +FUEL CENTER-RX, LAKE ZURICH</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -830,7 +830,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #542 +RX, BANNOCKBURN</t>
+          <t>MARIANO'S #519 +RX, AURORA</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -838,7 +838,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>17630 W BLUEMOUND</t>
+          <t>PICK #871 +RX, KENOSHA-NORTH</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -853,7 +853,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5600 SPRING ST</t>
+          <t>1001 E GENEVA SQUARE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -861,7 +861,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3030 N BROADWAY #100</t>
+          <t>678 N YORK STREET</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -869,7 +869,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1900 S CUMBERLAND DR</t>
+          <t>1350 EAST ROUTE 22</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -877,7 +877,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2999 WAUKEGAN RD</t>
+          <t>3025 E NEW YORK ST</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -885,7 +885,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Uv69q4HmCNQ2</t>
+          <t>2811 - 18TH STREET</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -900,7 +900,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/vkH7vLz9Zrx</t>
+          <t>https://goo.gl/maps/Tbkoc8cC9Nr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -908,7 +908,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/bMv5fDgQsNT2</t>
+          <t>https://goo.gl/maps/uREK7RJVhDC2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -916,7 +916,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/39qeNV6tuWU2</t>
+          <t>https://goo.gl/maps/72wfaM4QJ2s</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -924,7 +924,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/iQpQKzHwQVT2</t>
+          <t>https://goo.gl/maps/4LdNPuLeAJs</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -932,7 +932,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>https://goo.gl/maps/tq1opM5rw242</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -951,7 +951,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON SECOND FLOOR REG #4</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -961,7 +961,11 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>SET UP ON REG #4</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -982,18 +986,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>@ Store,
-Equip</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4:00 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
@@ -1012,21 +1019,13 @@
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>FULL STORE RESET-REMAPPED</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
@@ -1040,7 +1039,8 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store,
+Sante Fe, Equip</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1058,64 +1058,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Driver,
 Red Van</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Greg</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2nd week</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>3:45 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
@@ -1124,10 +1099,16 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Driver,
+White Camry,
+Rx</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
     </row>
@@ -1143,14 +1124,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Driver,
+Gold Camry</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1160,8 +1146,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Driver,
-Altima</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1172,26 +1157,13 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Joshua M</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Mai</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
@@ -1201,10 +1173,15 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
@@ -1220,28 +1197,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Greg</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2nd DC5 Financial</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2nd week</t>
+          <t>(w/ Trevor)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1252,22 +1225,26 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
@@ -1276,7 +1253,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -1295,19 +1272,23 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1319,22 +1300,27 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>(w/ Trevor),
+Rx</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
@@ -1343,7 +1329,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1362,26 +1348,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
@@ -1390,26 +1377,27 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Robyn</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2nd week</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
@@ -1418,12 +1406,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2nd week</t>
+          <t>After Aurora</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -1441,24 +1429,30 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Optima,
+Supv Rx</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1469,29 +1463,25 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
+          <t>Via</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>Driver,
+Red Van</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -1502,7 +1492,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -1514,25 +1504,33 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
@@ -1541,7 +1539,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1552,19 +1550,15 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
@@ -1573,10 +1567,15 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
@@ -1585,30 +1584,33 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
@@ -1617,31 +1619,27 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+2nd Rx</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
@@ -1650,14 +1648,10 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
@@ -1666,29 +1660,33 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
@@ -1697,31 +1695,26 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
@@ -1730,14 +1723,10 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Until 9:00</t>
-        </is>
-      </c>
+          <t>Joshua M</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
     </row>
@@ -1747,26 +1736,22 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>(w/ Carlie)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1777,7 +1762,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1788,19 +1773,15 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
@@ -1809,14 +1790,10 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
@@ -1826,27 +1803,23 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>DHILLON'S BP, MAYVILLE</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>@ Store,
-Rx</t>
+1st Rx</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1857,7 +1830,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -1868,19 +1841,15 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
@@ -1889,7 +1858,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
@@ -1904,19 +1873,19 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1400 HORICON ST</t>
+          <t>5:15 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1932,7 +1901,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -1943,19 +1912,15 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
@@ -1964,14 +1929,10 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Robyn</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>2nd week</t>
-        </is>
-      </c>
+          <t>Via</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
@@ -1983,19 +1944,19 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/UAmrX3SR6jD2</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2011,29 +1972,28 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Josh S</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>(w/ Carlie)</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -2044,10 +2004,15 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
     </row>
@@ -2059,25 +2024,24 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5:00 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2088,31 +2052,31 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>@ Store,
 Supv Rx</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
@@ -2121,12 +2085,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2138,17 +2102,21 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #204, KENOSHA</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Josh S</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2164,18 +2132,31 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -2188,41 +2169,64 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>2801 14TH PLACE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Wyatt</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Wyatt</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -2232,22 +2236,13 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>@ Store
-(w/ Trevor)</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/qpmx5KbNekBXgfTh9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2258,17 +2253,13 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -2280,51 +2271,26 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>@ Store
-(w/ Carlie)</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>6:15 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2 SISTERS PIGGLY WIGGLY #266, MARKESAN</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -2336,14 +2302,27 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2351,7 +2330,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
@@ -2359,7 +2338,7 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #092, HARTLAND</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -2367,7 +2346,7 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>450 N MARGARET ST</t>
+          <t>AURORA OUTPATIENT RX #1179, KENOSHA</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -2379,15 +2358,22 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>METRO #892 +RX, MENOMONEE FALLS - 
-COUNTY LINE RD</t>
+          <t>*PERISHABLE INVENTORY</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2395,7 +2381,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>*FIRST INVENTORY WITH BADGER</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -2403,7 +2389,7 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>505 SOUTH COTTONWOOD</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -2411,7 +2397,7 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/nVgmJAwKdEjhqQAt6</t>
+          <t>7540 22ND AVE</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -2423,10 +2409,14 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2434,7 +2424,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>N95 W18351 COUNTY LINE RD</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2442,7 +2432,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #493, RACINE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
@@ -2450,13 +2440,17 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/3fKEhu9Q6Q52</t>
+          <t>AURORA OUTPATIENT RX #1002, MILWAUKEE</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/66CQ3FRNP6o</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -2466,10 +2460,14 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2477,7 +2475,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/KutaqrX9XEx</t>
+          <t>METCALFE'S MARKET #560, WAUWATOSA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2485,7 +2483,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3441 SPRING ST</t>
+          <t>PIGGLY WIGGLY #142, SUSSEX</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -2493,26 +2491,14 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>RESETS-REMAPPED</t>
+          <t>6901 W EDGERTON AVENUE</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
     </row>
@@ -2521,18 +2507,26 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SET UP LAST REG BY SELF C/O</t>
+          <t>6700 W STATE ST</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2540,29 +2534,32 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/8i7XHemjTpL2</t>
+          <t>N63 W23735 MAIN ST</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/HkLUg5WJ5E32</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>@ Store,
-Optima</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -2573,18 +2570,26 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DHILLON'S STATION HUSTIS</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+          <t>https://goo.gl/maps/hbUxBiCRdt72</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2592,42 +2597,18 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW </t>
+          <t>https://maps.app.goo.gl/UHB7SgmVy27KNfWS7</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
     </row>
@@ -2636,57 +2617,49 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>326 W JUNEAU ST</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store  </t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
     </row>
@@ -2695,13 +2668,21 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/2MvPuCPioicrHiKc6</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Louisa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
@@ -2719,45 +2700,41 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #9570, RACINE</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
     </row>
@@ -2766,9 +2743,21 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
@@ -2777,54 +2766,34 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>(w/ Trevor)</t>
-        </is>
-      </c>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2731 DURAND AVE</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
     </row>
@@ -2835,17 +2804,17 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Serena</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2856,37 +2825,33 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/boUkpED44a62</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1335, SUMMIT</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
@@ -2896,52 +2861,40 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>5:30 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>36500 AURORA DRIVE, SUITE 100</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
@@ -2951,75 +2904,38 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Driver,
-White Camry</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Nick</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Milwaukee Office</t>
+          <t>https://goo.gl/maps/ZCBnSuQHz8ghtBeU6</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -3032,53 +2948,48 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5:15 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Driver,
-White Camry</t>
-        </is>
-      </c>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>After Metro</t>
-        </is>
-      </c>
+          <t>NOTE FROM KIM FROM LAST INV RX WILL BE MOVING ACROSS THE HALL.  SUITE NUMBER MAY BE DIFFERENT.</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
     </row>
@@ -3088,31 +2999,51 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>After Metcalfes</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
         <is>
           <t>7)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>CONDON OIL #185, RIPON</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>APPROX 9:00 AM START</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -3125,26 +3056,14 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Robyn</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2nd week</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -3153,13 +3072,17 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>641 E OSHKOSH ST</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -3172,41 +3095,33 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>PIGGLY WIGGLY #209, KENOSHA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>4:30 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>https://goo.gl/maps/XYUwgvQ4nxz</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>AURORA VISION #1162, SUMMIT</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
@@ -3219,27 +3134,19 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>7600 PERSHING BLVD</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>4:15 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
@@ -3247,13 +3154,17 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1067, HARTLAND</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>36500 AURORA DR, SUITE 130</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -3266,31 +3177,19 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SULLIVAN'S FOODS #225, FREEPORT</t>
+          <t>https://goo.gl/maps/JzRgLG7fbbR2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
@@ -3298,13 +3197,17 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>600 WALNUT RIDGE DR</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/uVd8GmA8otk</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
@@ -3317,31 +3220,19 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2002 W GALENA AVE</t>
+          <t>4:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>(w/ Carlie)</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>DHILLON'S BP, MARKESAN</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -3349,13 +3240,17 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/sZu3Qrsu6zC2</t>
+          <t>CONDON OIL #280, RIPON</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>USE MEDICAL OFFICE ENTRANCE.  FOLLOW EMERG ROOM ARROW IN PARKING LOT</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -3366,39 +3261,27 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/YcFP9FTjTEs94iQh7</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>N1894 WI-44 (HWY 44 &amp; 73)</t>
+          <t>PIGGLY WIGGLY #038, MENASHA</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1105 W FOND DU LAC ST</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
@@ -3412,57 +3295,58 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>WE SET UP IN THE BACKROOM BY END OF FROZEN AISLES</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/uRQ5w6AXAun5KEMW7</t>
+          <t>1151 MIDWAY RD</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/n7ESHm7AS732</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Gold Camry available, Equip</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3471,30 +3355,32 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Driver,
+White Camry
+(w/ Trevor)</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>4:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+          <t>https://goo.gl/maps/ufFM5TycoD42</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -3503,8 +3389,16 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
@@ -3516,34 +3410,54 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Joshua M</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>LIQUOR &amp; SMALL RESETS-REMAPPED</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Gold Camry, Equip</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
@@ -3555,48 +3469,43 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Driver,
-Tan Camry</t>
-        </is>
-      </c>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
@@ -3611,47 +3520,34 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>@ Store
-(w/ Trevor)</t>
-        </is>
-      </c>
+          <t>4:45 am meet at Slinger Piggly Wiggly (Lashaun/Carlie/Trevor)</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -3667,7 +3563,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3678,40 +3574,23 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>@ Store
-(w/ Carlie)</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>DHILLON'S HARTLAND VILLAGE MART</t>
-        </is>
-      </c>
+      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
@@ -3723,42 +3602,46 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>OPEN PANTRY #605, BAYSIDE</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>301 E CAPITOL DR</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
@@ -3770,38 +3653,42 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>(w/ Carlie)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>501 W BROWN DEER RD</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>(w/ Trevor to Slinger)</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/D7P2Btvsg3y</t>
-        </is>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -3817,35 +3704,36 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Via</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/pQaSRAn88Vh6DAQ58</t>
-        </is>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>5:15 AM MEET OFFICE</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3862,53 +3750,33 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Tan Camry available, Equip</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
@@ -3921,48 +3789,32 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -3977,41 +3829,36 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>OPEN PANTRY #612, BROOKFIELD</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>DHILLON'S BP, NEOSHO</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>@ Store,
-After Aurora</t>
-        </is>
-      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
@@ -4025,24 +3872,32 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>17235 W BLUEMOUND RD</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>446 S SCHUYER ST</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4060,24 +3915,32 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #208, DELAVAN</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/awRYbmypZ4H2</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/cqKUT41W2wM2</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4095,27 +3958,35 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1414 E GENEVA ST</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Louisa</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>4:45 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
+      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -4130,40 +4001,35 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/hixkUheCekD2</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Driver,
-Sante Fe, Equip</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -4182,31 +4048,27 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>OPEN PANTRY #614, MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
+          <t>Serena</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -4220,36 +4082,44 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>3100 S 76TH ST</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
+          <t>Taya</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>DHILLON'S STATION 51 LLC, JANESVILLE</t>
-        </is>
-      </c>
+      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
@@ -4263,16 +4133,24 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/fpg1rAd58h22</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -4280,11 +4158,7 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>1620 W US HWY 14</t>
-        </is>
-      </c>
+      <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -4298,9 +4172,21 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -4311,11 +4197,7 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/AMes3hiS3DN1CYZx6</t>
-        </is>
-      </c>
+      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
@@ -4329,40 +4211,32 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>White Camry available, Equip</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>5:15 AM MEET WATERTOWN PLANK</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride - Go straight to the store</t>
-        </is>
-      </c>
+      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -4376,28 +4250,28 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Josh S</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
@@ -4415,45 +4289,33 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
@@ -4466,38 +4328,33 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>DHILLON'S STATION HWY 33, HARTFORD</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>@ Store
-(w/ Trevor)</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
@@ -4510,32 +4367,32 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>W346 LUEDTKE LANE</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
@@ -4549,32 +4406,32 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/sBbGZTSeFYGcwxAe7</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
@@ -4588,9 +4445,21 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
@@ -4600,22 +4469,9 @@
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Driver,
-White Camry</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
@@ -4628,47 +4484,33 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Wyatt</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>Driver,
-Tan Camry, Equip</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>@ Store
-(w/ Carlie)</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
@@ -4676,196 +4518,6 @@
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>After Dhillons</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
